--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -485,6 +485,291 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7b1d7504c6</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HR Coordinator</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Samcom Technologies</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Hr.officer@samcom.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Corporate Directory</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>d8d5ad91c3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Document Controller</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Al Naboodah Construction</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>recruitment@alnaboodah.ae</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Corporate Directory</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2afcaa3f5b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Emaar Properties</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>hr@emaar.ae</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Corporate Directory</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>f565043e75</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Admin Assistant</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Damac Properties</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>deepak.sharma@damacgroup.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Corporate Directory</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>acb86c2aea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aramex Dubai</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>regional.talent@aramex.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Corporate Directory</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
         </is>
       </c>
     </row>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +50,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,14 +58,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,8 +452,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
@@ -768,6 +805,1146 @@
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>501fb8aa88</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>HR Executive</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Al Futtaim Group</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>recruitment@alfuttaim.ae</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5dbe775491</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Project Engineer</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Ascon Contracting</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>careers@etaascon.com</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>a0ce8527fa</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Procurement Officer</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sobha Realty</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>talent.acquisition@sobha-me.com</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>d41330d80d</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Customer Service Specialist</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>FlyDubai</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>jobs.cabincrew@flydubai.com</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>661dbb118a</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IT Support Technician</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Sharaf DG</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>hr.support@sharafdg.com</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5821f2cd9a</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Digital Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Chalhoub Group</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>careers@chalhoub.com</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2f5a6670c9</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DP World Dubai</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>recruitment.dxb@dpworld.com</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>a259082806</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Accountant</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Apparel Group</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>careers@appareluae.com</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>f08e7923f6</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Sales Coordinator</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Danube Properties</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>hr@danubeproperties.ae</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>b3cf72fb10</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>QHSE Officer</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Dutco Balfour Beatty</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>recruitment@dutco.com</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>9530a797ea</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Public Relations Officer (PRO)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>VFS Global Dubai</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>pro.recruitment@vfsglobal.com</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>50f3314469</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>L&amp;D Trainer</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Jumeirah Group</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>hospitality.talent@jumeirah.com</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>41d520285d</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Quantity Surveyor</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Nakheel</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>careers@nakheel.com</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>86679c3c48</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Leasing Agent</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Al Ghurair Investment</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>hr.talent@al-ghurair.com</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>fb3a4f1640</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Mechanical Engineer</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Khansaheb Civil Engineering</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>careers@khansaheb.ae</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>455d8b79d5</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Warehouse Administrator</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Landmark Group</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>recruitment.logistics@landmarkgroup.com</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>c27e1585da</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Mediclinic Middle East</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>hr.recruitment@mediclinic.ae</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>6ce1f08e11</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Content Creator</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Noon.com</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>careers.talent@noon.com</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2964dc0bdc</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Financial Analyst</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Mashreq Bank</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>recruitment@mashreq.com</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>6f7b98231d</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>BIM Modeler</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Habtoor Leighton Group</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>careers@hlgroup.com</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Minimum 5 Years</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Verified Commercial Feed</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Relevant Degree or Certification</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>15-06-2026</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>15-06-2026</t>
         </is>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Job Database" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="22-06-2026" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,9 @@
       <name val="Segoe UI"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -50,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -72,11 +76,17 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -86,6 +96,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1953,4 +1966,645 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cabin Crew Opportunities (Emirates)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/cabin-crew-opportunities-at-emirates-4422780969</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1 week ago</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Customer Service Roles (Emirates)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-roles-at-emirates-4412226959</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Retail Sales Associate (PUMA Group)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/retail-sales-associate-at-puma-group-4292538398</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Officer, Customer Service - Dubai (First Abu Dhabi Bank (FAB))</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/officer-customer-service-dubai-at-first-abu-dhabi-bank-fab-4361410449</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1 week ago</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cabin Services Assistant (Emirates)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/cabin-services-assistant-at-emirates-4240426528</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Team Member (Emirates Flight Catering)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/team-member-at-emirates-flight-catering-4423371025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Teller (ADIB - Abu Dhabi Islamic Bank)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/teller-at-adib-abu-dhabi-islamic-bank-4422681259</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sales Representative - Dubai (Etihad)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/sales-representative-dubai-at-etihad-4419686413</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1 week ago</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SAINT LAURENT Client Advisor (Saint Laurent)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/saint-laurent-client-advisor-at-saint-laurent-4419695525</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2 weeks ago</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Customer Support Specialist (ADIB - Abu Dhabi Islamic Bank)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/customer-support-specialist-at-adib-abu-dhabi-islamic-bank-4427183556</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See LinkedIn job description</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Jobs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Degree / Experience</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1 week ago</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2037,7 +2037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cabin Crew Opportunities (Emirates)</t>
+          <t>Workshop Planning Engineer (Air Arabia)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,22 +2047,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/cabin-crew-opportunities-at-emirates-4422780969</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-planning-engineer-at-air-arabia-4404092820</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer Service Roles (Emirates)</t>
+          <t>Product Engineer Commissioning &amp; Software - Global Data Center Segment (Eaton)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-roles-at-emirates-4412226959</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/product-engineer-commissioning-software-global-data-center-segment-at-eaton-4403832587</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Retail Sales Associate (PUMA Group)</t>
+          <t>Regional Technical Manager (Boskalis)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2161,22 +2161,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/retail-sales-associate-at-puma-group-4292538398</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-technical-manager-at-boskalis-4423984252</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Officer, Customer Service - Dubai (First Abu Dhabi Bank (FAB))</t>
+          <t>Executive - Production (Himalaya Wellness Europe)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/officer-customer-service-dubai-at-first-abu-dhabi-bank-fab-4361410449</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-production-at-himalaya-wellness-europe-4431684992</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cabin Services Assistant (Emirates)</t>
+          <t>Component Rebuild Center (CRC) Supervisor (Al Marwan Group)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/cabin-services-assistant-at-emirates-4240426528</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/component-rebuild-center-crc-supervisor-at-al-marwan-group-4430580648</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team Member (Emirates Flight Catering)</t>
+          <t>Senior Marketing Manager (Heavy Machinery/Aluminum/Chemicals Industry) (TASC Outsourcing)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2332,22 +2332,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/team-member-at-emirates-flight-catering-4423371025</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-marketing-manager-heavy-machinery-aluminum-chemicals-industry-at-tasc-outsourcing-4430389780</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Teller (ADIB - Abu Dhabi Islamic Bank)</t>
+          <t>Regional Sales Manager (Giesecke+Devrient)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2389,22 +2389,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/teller-at-adib-abu-dhabi-islamic-bank-4422681259</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-giesecke%2Bdevrient-4430547775</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sales Representative - Dubai (Etihad)</t>
+          <t>Regional Sales Manager (TALENTMATE)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2446,22 +2446,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/sales-representative-dubai-at-etihad-4419686413</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-talentmate-4431700836</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAINT LAURENT Client Advisor (Saint Laurent)</t>
+          <t>Area Sales Manager (Lucy Group Ltd)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2503,22 +2503,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/saint-laurent-client-advisor-at-saint-laurent-4419695525</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/area-sales-manager-at-lucy-group-ltd-4363180893</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2 weeks ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Customer Support Specialist (ADIB - Abu Dhabi Islamic Bank)</t>
+          <t>HR Operations Manager (Element MEA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Apply directly on LinkedIn: https://ae.linkedin.com/jobs/view/customer-support-specialist-at-adib-abu-dhabi-islamic-bank-4427183556</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-operations-manager-at-element-mea-4431685049</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>See LinkedIn job description</t>
+          <t>See job details on LinkedIn</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sourced via LinkedIn Jobs</t>
+          <t>Sourced via LinkedIn Professional Index</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Relevant Degree / Experience</t>
+          <t>Relevant Professional Degree</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2595,10 +2595,238 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1 week ago</t>
+          <t>Posted Today</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sales Manager/Senior Sales Manager (ONE BROKER GROUP)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-manager-senior-sales-manager-at-one-broker-group-4428934943</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Joinery Production Manager (Spring Tech)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/joinery-production-manager-at-spring-tech-4430505832</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Business Operations Manager (SmartChoice International GCC)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/business-operations-manager-at-smartchoice-international-gcc-4428951429</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F&amp;B Supervisor (Discovery Dunes Golf Club)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/f-b-supervisor-at-discovery-dunes-golf-club-4430382394</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2037,7 +2037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Workshop Planning Engineer (Air Arabia)</t>
+          <t>Engineering Manager – Business Platforms (Fintech) (eMagine Solutions)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-planning-engineer-at-air-arabia-4404092820</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-%E2%80%93-business-platforms-fintech-at-emagine-solutions-4431689534</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Product Engineer Commissioning &amp; Software - Global Data Center Segment (Eaton)</t>
+          <t>Senior Manager IT (SKY ONE)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/product-engineer-commissioning-software-global-data-center-segment-at-eaton-4403832587</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-manager-it-at-sky-one-4431721278</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Regional Technical Manager (Boskalis)</t>
+          <t>Manager - Sub station (DAMAC Digital)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-technical-manager-at-boskalis-4423984252</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-sub-station-at-damac-digital-4428907481</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Executive - Production (Himalaya Wellness Europe)</t>
+          <t>Regional Sales Manager (Apollo Tyres Ltd)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-production-at-himalaya-wellness-europe-4431684992</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-apollo-tyres-ltd-4431663312</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Component Rebuild Center (CRC) Supervisor (Al Marwan Group)</t>
+          <t>Associate Director (Hydrogen Group)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/component-rebuild-center-crc-supervisor-at-al-marwan-group-4430580648</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-director-at-hydrogen-group-4430960804</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2322,7 +2322,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Marketing Manager (Heavy Machinery/Aluminum/Chemicals Industry) (TASC Outsourcing)</t>
+          <t>Customer Service Lead (Arabic Speaker) (Nathan &amp; Nathan)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-marketing-manager-heavy-machinery-aluminum-chemicals-industry-at-tasc-outsourcing-4430389780</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-lead-arabic-speaker-at-nathan-nathan-4431657450</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Regional Sales Manager (Giesecke+Devrient)</t>
+          <t>Store Manager | Emirati Talent (Majid Al Futtaim)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-giesecke%2Bdevrient-4430547775</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-emirati-talent-at-majid-al-futtaim-4428910310</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Regional Sales Manager (TALENTMATE)</t>
+          <t>Division Manager (WORKSPACE)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-talentmate-4431700836</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/division-manager-at-workspace-4428932521</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2493,7 +2493,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Area Sales Manager (Lucy Group Ltd)</t>
+          <t>Senior Facilities Manager (KAIZEN Asset Management Services)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/area-sales-manager-at-lucy-group-ltd-4363180893</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-facilities-manager-at-kaizen-asset-management-services-4431674492</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HR Operations Manager (Element MEA)</t>
+          <t>Head - Digital Transformation &amp; AI (AMICORP WEALTH SERVICES)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-operations-manager-at-element-mea-4431685049</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-digital-transformation-ai-at-amicorp-wealth-services-4431617400</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2599,234 +2599,6 @@
         </is>
       </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sales Manager/Senior Sales Manager (ONE BROKER GROUP)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-manager-senior-sales-manager-at-one-broker-group-4428934943</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>See job details on LinkedIn</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sourced via LinkedIn Professional Index</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Relevant Professional Degree</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>ASAP</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Posted Today</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Joinery Production Manager (Spring Tech)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/joinery-production-manager-at-spring-tech-4430505832</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>See job details on LinkedIn</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sourced via LinkedIn Professional Index</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Relevant Professional Degree</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ASAP</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Posted Today</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Business Operations Manager (SmartChoice International GCC)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/business-operations-manager-at-smartchoice-international-gcc-4428951429</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>See job details on LinkedIn</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sourced via LinkedIn Professional Index</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Relevant Professional Degree</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ASAP</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Posted Today</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>F&amp;B Supervisor (Discovery Dunes Golf Club)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Dubai, UAE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/f-b-supervisor-at-discovery-dunes-golf-club-4430382394</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>See job details on LinkedIn</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sourced via LinkedIn Professional Index</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Relevant Professional Degree</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>ASAP</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Posted Today</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2604,861 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sales Director (UNISON INTERNATIONAL CONSULTING (The Recruitment Company))</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-director-at-unison-international-consulting-the-recruitment-company-4430545668</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Manager - Corporate Quality Assurance (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-corporate-quality-assurance-at-roads-and-transport-authority-4428908378</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Strategy Director (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/strategy-director-at-talentmate-4431625419</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Industry Manager (Water, Waste Water &amp; Power) (Endress+Hauser Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/industry-manager-water-waste-water-power-at-endress%2Bhauser-group-4431691016</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>General Manager (Confidential)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-manager-at-confidential-4428920823</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Spa Director (Soneva)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/spa-director-at-soneva-4431668111</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Business Development Manager - Institutional Finance / Crypto (Ceffu)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-business-development-manager-institutional-finance-crypto-at-ceffu-4430348990</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Marketing And Brand Director (Synolon Systems)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/marketing-and-brand-director-at-synolon-systems-4428952331</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Operations (Company Management Services) (AMICORP WEALTH SERVICES)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-operations-company-management-services-at-amicorp-wealth-services-4431608753</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Head of Social Dominance And Viral Growth (Synolon Systems)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-social-dominance-and-viral-growth-at-synolon-systems-4428962237</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Statistics Manager -(Emirati) (Talents Tide)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-statistics-manager-emirati-at-talents-tide-4430572779</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Commercial Property Manager (Savills Middle East)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/commercial-property-manager-at-savills-middle-east-4431676730</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Supervisor - Gym Cafeteria (AB Fitness UAE)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-gym-cafeteria-at-ab-fitness-uae-4431712834</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Strategic Sourcing &amp; Tender Manager (with Russian language) (AM.PM)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/strategic-sourcing-tender-manager-with-russian-language-at-am-pm-4428937760</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Lead Document Controller (Arada)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-document-controller-at-arada-4428951227</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Professional Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -2037,7 +2037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Engineering Manager – Business Platforms (Fintech) (eMagine Solutions)</t>
+          <t>IT Application Administrator (ENOC)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-%E2%80%93-business-platforms-fintech-at-emagine-solutions-4431689534</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-application-administrator-at-enoc-4431670888</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Manager IT (SKY ONE)</t>
+          <t>Admin Executive - Interior Fit-Out Firm - Dubai Location - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-manager-it-at-sky-one-4431721278</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-interior-fit-out-firm-dubai-location-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4430371794</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2151,7 +2151,8 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Manager - Sub station (DAMAC Digital)</t>
+          <t>Title
+                    Locum - Stores Assistant (Mediclinic Middle East)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2161,7 +2162,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-sub-station-at-damac-digital-4428907481</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/title%0A-%0A-%0A-locum-stores-assistant-at-mediclinic-middle-east-4430599947</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2176,7 +2177,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2208,7 +2209,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Regional Sales Manager (Apollo Tyres Ltd)</t>
+          <t>Admin Assistant, Sales  -  Time Out (ITP Media Group)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2218,7 +2219,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-sales-manager-at-apollo-tyres-ltd-4431663312</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-assistant-sales-time-out-at-itp-media-group-4430800211</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2233,7 +2234,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2265,7 +2266,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Director (Hydrogen Group)</t>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2275,7 +2276,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-director-at-hydrogen-group-4430960804</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4430363933</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2290,7 +2291,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2322,7 +2323,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Customer Service Lead (Arabic Speaker) (Nathan &amp; Nathan)</t>
+          <t>Front Office Manager (Confidential)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2332,7 +2333,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-lead-arabic-speaker-at-nathan-nathan-4431657450</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-confidential-4428926436</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2347,7 +2348,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2379,7 +2380,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Store Manager | Emirati Talent (Majid Al Futtaim)</t>
+          <t>Executive Assistant | Corporate Services (Al-Futtaim)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2389,7 +2390,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-emirati-talent-at-majid-al-futtaim-4428910310</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-corporate-services-at-al-futtaim-4431665882</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2404,7 +2405,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2436,7 +2437,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Division Manager (WORKSPACE)</t>
+          <t>SENIOR REAL ESTATE ADMINISTRATOR (Zenith Technologies)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2446,7 +2447,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/division-manager-at-workspace-4428932521</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-real-estate-administrator-at-zenith-technologies-4428924814</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2461,7 +2462,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2493,7 +2494,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Facilities Manager (KAIZEN Asset Management Services)</t>
+          <t>Facilities Coordinator - CRE (Abdulla Al Rostamani Properties L.L.C.)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2503,7 +2504,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-facilities-manager-at-kaizen-asset-management-services-4431674492</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-coordinator-cre-at-abdulla-al-rostamani-properties-l-l-c-4421696752</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2518,7 +2519,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2550,7 +2551,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Head - Digital Transformation &amp; AI (AMICORP WEALTH SERVICES)</t>
+          <t>Warehouse Assistant (ShowTex Middle East)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2560,7 +2561,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-digital-transformation-ai-at-amicorp-wealth-services-4431617400</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-at-showtex-middle-east-4431658614</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2575,7 +2576,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2607,7 +2608,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sales Director (UNISON INTERNATIONAL CONSULTING (The Recruitment Company))</t>
+          <t>SKIMS Coming to Mirdif City Centre – We’re Hiring! (Al Tayer Insignia)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2617,7 +2618,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-director-at-unison-international-consulting-the-recruitment-company-4430545668</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/skims-coming-to-mirdif-city-centre-%E2%80%93-we%E2%80%99re-hiring%21-at-al-tayer-insignia-4428925504</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2632,7 +2633,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2664,7 +2665,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manager - Corporate Quality Assurance (Roads and Transport Authority)</t>
+          <t>Hiredesk Coordinator (CDHorizon United Arab Emirates)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2674,7 +2675,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-corporate-quality-assurance-at-roads-and-transport-authority-4428908378</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hiredesk-coordinator-at-cdhorizon-united-arab-emirates-4431640587</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2689,7 +2690,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2721,7 +2722,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Strategy Director (TALENTMATE)</t>
+          <t>D365 ERP Functional Consultant (AIR (Advanced Inhalation Rituals))</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2731,7 +2732,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/strategy-director-at-talentmate-4431625419</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/d365-erp-functional-consultant-at-air-advanced-inhalation-rituals-4428950452</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2746,7 +2747,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2778,7 +2779,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Industry Manager (Water, Waste Water &amp; Power) (Endress+Hauser Group)</t>
+          <t>Secretary (Confidential)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2788,7 +2789,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/industry-manager-water-waste-water-power-at-endress%2Bhauser-group-4431691016</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/secretary-at-confidential-4428934266</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2803,7 +2804,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2835,7 +2836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>General Manager (Confidential)</t>
+          <t>Warranty Officer (TALENTMATE)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2845,7 +2846,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-manager-at-confidential-4428920823</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warranty-officer-at-talentmate-4431692984</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2860,7 +2861,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2892,7 +2893,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spa Director (Soneva)</t>
+          <t>Leasing Development Manager (Confidential)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2902,7 +2903,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/spa-director-at-soneva-4431668111</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/leasing-development-manager-at-confidential-4431645418</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2917,7 +2918,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2949,7 +2950,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Business Development Manager - Institutional Finance / Crypto (Ceffu)</t>
+          <t>Store Manager -Modora (Home Division) (GMG)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2959,7 +2960,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-business-development-manager-institutional-finance-crypto-at-ceffu-4430348990</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-modora-home-division-at-gmg-4430580642</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2974,7 +2975,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3006,7 +3007,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marketing And Brand Director (Synolon Systems)</t>
+          <t>Personal Secretary (Hire Rightt - Executive Search &amp; HR Advisory)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3016,7 +3017,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/marketing-and-brand-director-at-synolon-systems-4428952331</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-secretary-at-hire-rightt-executive-search-hr-advisory-4430392883</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3031,7 +3032,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3063,7 +3064,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Operations (Company Management Services) (AMICORP WEALTH SERVICES)</t>
+          <t>Onsite Logistician- Fixed Term (12 months+) (Siemens Energy)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3073,7 +3074,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-operations-company-management-services-at-amicorp-wealth-services-4431608753</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/onsite-logistician-fixed-term-12-months%2B-at-siemens-energy-4430502024</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3088,7 +3089,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3120,7 +3121,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Head of Social Dominance And Viral Growth (Synolon Systems)</t>
+          <t>Controlling &amp; Accounting Coordinator (Stellantis Middle East &amp; Africa)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3130,7 +3131,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-social-dominance-and-viral-growth-at-synolon-systems-4428962237</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/controlling-accounting-coordinator-at-stellantis-middle-east-africa-4428942503</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3145,7 +3146,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3177,7 +3178,8 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Statistics Manager -(Emirati) (Talents Tide)</t>
+          <t>Title
+                    Unit Manager - Accident &amp; Emergency (Mediclinic Middle East)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3187,7 +3189,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-statistics-manager-emirati-at-talents-tide-4430572779</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/title%0A-%0A-%0A-unit-manager-accident-emergency-at-mediclinic-middle-east-4430809173</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3202,7 +3204,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3234,7 +3236,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Commercial Property Manager (Savills Middle East)</t>
+          <t>Senior Electrical Engineer (MEP) (Professional Engineers Electro Mechanical Contracting (PECO MEP))</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3244,7 +3246,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/commercial-property-manager-at-savills-middle-east-4431676730</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-electrical-engineer-mep-at-professional-engineers-electro-mechanical-contracting-peco-mep-4428906566</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3259,7 +3261,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3291,7 +3293,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Supervisor - Gym Cafeteria (AB Fitness UAE)</t>
+          <t>Manager - Sub station (DAMAC Digital)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3301,7 +3303,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-gym-cafeteria-at-ab-fitness-uae-4431712834</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-sub-station-at-damac-digital-4428907481</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3316,7 +3318,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3348,7 +3350,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Strategic Sourcing &amp; Tender Manager (with Russian language) (AM.PM)</t>
+          <t>IT Manager (Connexa Recruitment)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3358,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/strategic-sourcing-tender-manager-with-russian-language-at-am-pm-4428937760</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-manager-at-connexa-recruitment-4431635810</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3373,7 +3375,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3405,7 +3407,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lead Document Controller (Arada)</t>
+          <t>F&amp;B Supervisor (Discovery Dunes Golf Club)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3415,7 +3417,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-document-controller-at-arada-4428951227</t>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/f-b-supervisor-at-discovery-dunes-golf-club-4430382394</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3430,7 +3432,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Relevant Professional Degree</t>
+          <t>Relevant Background / Degree</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Job Database" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="22-06-2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="23-06-2026" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3464,4 +3465,1501 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Title
+                    Locum - Stores Assistant (Mediclinic Middle East)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/title%0A-%0A-%0A-locum-stores-assistant-at-mediclinic-middle-east-4430599947</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IT Application Administrator (ENOC)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-application-administrator-at-enoc-4431670888</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Support - Wirelines Services (Baker Hughes)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-support-wirelines-services-at-baker-hughes-4432072782</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Executive Assistant | Corporate Services (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-corporate-services-at-al-futtaim-4431665882</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warehouse In-Charge (Net2Source (N2S))</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-in-charge-at-net2source-n2s-4432200411</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4430853925</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (ARENGY)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-arengy-4431204341</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Admin Assistant, Sales  -  Time Out (ITP Media Group)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-assistant-sales-time-out-at-itp-media-group-4430800211</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Countersales Executive - Trucks Division (Galadari Heavy Equipment)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/countersales-executive-trucks-division-at-galadari-heavy-equipment-4432097489</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT Infrastructure &amp; Administration Lead (Confidential Jobs)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-infrastructure-administration-lead-at-confidential-jobs-4432078862</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Customer Service Assistant (MMI - Maritime and Mercantile International)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-assistant-at-mmi-maritime-and-mercantile-international-4431222071</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Construction Manager (Fit out) (Al Shirawi Interiors)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-fit-out-at-al-shirawi-interiors-4431673453</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Account Manager - Home Cleaning (Justlife)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/account-manager-home-cleaning-at-justlife-4431781241</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pre-Contract Estimator (First Point Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pre-contract-estimator-at-first-point-group-4428928980</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Manager IT (SKY ONE)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-manager-it-at-sky-one-4431721278</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sales Coordinator (Algedra)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-at-algedra-4430883602</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Renewal administrator (LNKD)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/renewal-administrator-at-lnkd-4431204198</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Supervisor - Workshop (Al Ghurair)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-workshop-at-al-ghurair-4429669864</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Associate Driver Operations (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-driver-operations-at-talentmate-4432077453</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Solution Specialist (Pine Labs UAE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/solution-specialist-at-pine-labs-uae-4432204190</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>HSEQ Manager (Impala Terminals)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hseq-manager-at-impala-terminals-4431672764</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Logistics Specialist (Orion Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-specialist-at-orion-group-4431207073</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Planner (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planner-at-mcdermott-international-ltd-4431708645</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Solar O&amp;M Engineer (Pactive Sustainable Solutions)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/solar-o-m-engineer-at-pactive-sustainable-solutions-4430867806</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Freight Forwarding Operations Executive (Meena Almadina Freight Broker LLC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Job Database" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="22-06-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="23-06-2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="24-06-2026" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4962,4 +4963,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Executive Assistant (La Capitale Real Estate)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-la-capitale-real-estate-4430887758</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Manager &amp; Executive Assistant - Part Time (Hays)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-executive-assistant-part-time-at-hays-4429821753</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>System Administrator (MINDTEL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/system-administrator-at-mindtel-4431214842</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Office Administrator (Infinix Innovations)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-at-infinix-innovations-4431225478</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ambassador (Floor Manager) (Dicetek LLC)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ambassador-floor-manager-at-dicetek-llc-4432475348</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sales Associate (Avensys Consulting)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-associate-at-avensys-consulting-4432519671</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Admin &amp; Logistics Coordinator (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-logistics-coordinator-at-tasc-outsourcing-4431481301</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant (C&amp;C Search)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-c-c-search-4432239265</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SOFTWARE SUPPORT ENGINEER (Dubai Careers - A Smart Dubai Initiative)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/software-support-engineer-at-dubai-careers-a-smart-dubai-initiative-4429812971</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sales Executive-B2B (INDEX Conferences &amp; Exhibitions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-executive-b2b-at-index-conferences-exhibitions-4429849113</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F&amp;B Service Assistant (Confidential Careers)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/f-b-service-assistant-at-confidential-careers-4429825748</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PA to the CEO (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pa-to-the-ceo-at-rtc1-recruitment-services-4429826141</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Civil Estimation Engineer (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-estimation-engineer-at-asia-prime-general-contracting-co-l-l-c-4429832110</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Financial Accounting Assistant Manager (UAEN) (Sundus)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/financial-accounting-assistant-manager-uaen-at-sundus-4432527879</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Go-To-Market Lead, Sub-Saharan Africa, MENAT and South Asia, Google for Education (Google)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/go-to-market-lead-sub-saharan-africa-menat-and-south-asia-google-for-education-at-google-4432231257</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Commercial Warehouse Advisor – Dubai (REMAX PREMIER DUBAI)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/commercial-warehouse-advisor-%E2%80%93-dubai-at-remax-premier-dubai-4429853065</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OFFICE (Business Centre) LEASING MANAGER (Magnum Opus Foundation)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-business-centre-leasing-manager-at-magnum-opus-foundation-4432218942</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Contract Manager (Khatib &amp; Alami)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/contract-manager-at-khatib-alami-4432282220</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Retail Operations Specialist (Beijing Foreign Enterprise Management Consultants Co.,Ltd.)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-operations-specialist-at-beijing-foreign-enterprise-management-consultants-co-ltd-4432235635</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Engineering Manager (HR Ways - Hiring Tech Talent)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-engineering-manager-at-hr-ways-hiring-tech-talent-4432541205</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Deputy Boutique Manager (Jaeger-LeCoultre)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/deputy-boutique-manager-at-jaeger-lecoultre-4431233414</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>HL Lab Manager (Sungrow MENA &amp; Central Asia)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hl-lab-manager-at-sungrow-mena-central-asia-4432440756</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HSE Engineer - Site (U+A)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hse-engineer-site-at-u%2Ba-4432453650</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Contracts Administrator / Contracts Engineer (SYSTRA Brasil)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/contracts-administrator-contracts-engineer-at-systra-brasil-4432272847</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Procurement Manager (Siemens Energy)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-manager-at-siemens-energy-4431207864</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -11,6 +11,7 @@
     <sheet name="22-06-2026" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="23-06-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="24-06-2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="25-06-2026" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6459,4 +6460,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Senior Office Admin / Operations Coordinator (Abdulla Al Ghurair Foundation)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-office-admin-operations-coordinator-at-abdulla-al-ghurair-foundation-4433051671</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cash Equity Middle Office, MENA (Assistant Vice President) (Jefferies)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cash-equity-middle-office-mena-assistant-vice-president-at-jefferies-4413422564</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive (Joud Coffee)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-at-joud-coffee-4431850320</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E-Commerce Manager (Electrolux Group)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/e-commerce-manager-at-electrolux-group-4432808636</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Administrative &amp; Office Manager (RTB House)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-office-manager-at-rtb-house-4431870272</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>System Administrator (ChillBase)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/system-administrator-at-chillbase-4429849227</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Oracle Fusion ERP Consultant - Dubai, UAE (Infosys)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/oracle-fusion-erp-consultant-dubai-uae-at-infosys-4429884592</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Store Assistant (LINK)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-assistant-at-link-4432604641</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IT Infrastructure &amp; Support Engineer (Dicetek LLC)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-infrastructure-support-engineer-at-dicetek-llc-4432897469</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Secretary (Meraki Group)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/secretary-at-meraki-group-4433072698</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Specialist - Procurement and Contracts (Dubai Healthcare City Authority, Government of Dubai)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/specialist-procurement-and-contracts-at-dubai-healthcare-city-authority-government-of-dubai-4431817813</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Personal Assistant (Payfuture)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-at-payfuture-4432544741</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Administrative Officer - Procurement (Binghatti)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-officer-procurement-at-binghatti-4432569059</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Site Interior / Project design Coordinator - 18,000 -20,000 AED (site and office based) - Dubai based - Looking for candidate with site supervision experience - (High end luxury interiors) (RIG (Recruitment International Group))</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-interior-project-design-coordinator-18-000-20-000-aed-site-and-office-based-dubai-based-looking-for-candidate-with-site-supervision-experience-high-end-luxury-interiors-at-rig-recruitment-international-group-4432570109</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dispute Resolution Supervisor (UAS International Trip Support)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dispute-resolution-supervisor-at-uas-international-trip-support-4429872201</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retail Executive (A. Lange &amp; Söhne)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-executive-at-a-lange-s%C3%B6hne-4431823834</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Accountant (OliOli® Children's Museum)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-accountant-at-olioli%C2%AE-children-s-museum-4429856713</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Support &amp; Maintenance Specialist (General Pension and Social Security Authority (GPSSA))</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/support-maintenance-specialist-at-general-pension-and-social-security-authority-gpssa-4433056715</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Assistant Income Auditor (Citymax Hotels by Landmark Group)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-income-auditor-at-citymax-hotels-by-landmark-group-4432616126</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>System Administrator (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/system-administrator-at-talentmate-4433009968</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Regional Manager, International Technology (Dubai based) (Papa Johns)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-manager-international-technology-dubai-based-at-papa-johns-4425599243</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Inventory Analyst (Caterpillar Inc.)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-analyst-at-caterpillar-inc-4432801248</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Licensed Aircraft Engineer - Base Maintenance (Emirates)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/licensed-aircraft-engineer-base-maintenance-at-emirates-4355906311</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MEP Site Specialist (Crystal Fit Contracting)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mep-site-specialist-at-crystal-fit-contracting-4432192488</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DIRECTOR DESIGN MANAGEMENT (Confidential)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/director-design-management-at-confidential-4429858434</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -12,6 +12,7 @@
     <sheet name="23-06-2026" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="24-06-2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="25-06-2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="26-06-2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7956,4 +7957,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Store Supervisor (KAFLAS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-supervisor-at-kaflas-4433537811</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Manager, Global Operations (Kerzner International)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-global-operations-at-kerzner-international-4430251282</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Assistant (KAFLAS)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-assistant-at-kaflas-4433531994</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4432934765</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Warehouse Clerk (Liebherr Group)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-clerk-at-liebherr-group-4432633039</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Registration Coordinator - Billing &amp; Invoicing (GLOMACS Training &amp; Consultancy)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/registration-coordinator-billing-invoicing-at-glomacs-training-consultancy-4432931774</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Junior Administrative Assistant (KAFLAS)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-administrative-assistant-at-kaflas-4433546607</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant (RIKAS Hospitality Group)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-rikas-hospitality-group-4432942475</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Office Administrator (Infinix Innovations)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-at-infinix-innovations-4432914184</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tendering and Bidding Specialist (Confidential)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/tendering-and-bidding-specialist-at-confidential-4430601318</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Administrative Support Specialist Cum HR (Ground Control Entertainment Co.)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-support-specialist-cum-hr-at-ground-control-entertainment-co-4430273360</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Executive - Admin &amp; Marketing (Dubai Integrated Economic Zones Authority)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-admin-marketing-at-dubai-integrated-economic-zones-authority-4433807910</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Project Coordinator (AlphaMind Group)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-at-alphamind-group-4432643245</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Assistant Manager - E-Commerce (Marketplace) (Landmark Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-e-commerce-marketplace-at-landmark-group-4430223187</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Project Coordinator - RCM &amp; Billing System Replacement (King’s College Hospital London, Dubai)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-rcm-billing-system-replacement-at-king%E2%80%99s-college-hospital-london-dubai-4430237281</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Account Manager (Hilti Emirates)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/account-manager-at-hilti-emirates-4433804193</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Billing and Invoicing Specialist (GLOMACS Training &amp; Consultancy)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/billing-and-invoicing-specialist-at-glomacs-training-consultancy-4430609409</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Junior Sales Coordinator - Tendering - Automotive Manufacturing - Dubai (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-sales-coordinator-tendering-automotive-manufacturing-dubai-at-sanvi-engineering-and-business-consulting-solutions-4432936450</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Assistant Manager - E-Commerce (Landmark Group)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-e-commerce-at-landmark-group-4430228104</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HR Admin and Operations (STARTRADER)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-admin-and-operations-at-startrader-4433085572</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LoA Coordinator (f/m/d) (Siemens Energy)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/loa-coordinator-f-m-d-at-siemens-energy-4432657820</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Customer Relationship Officer (ADIB - Abu Dhabi Islamic Bank)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-relationship-officer-at-adib-abu-dhabi-islamic-bank-4432958115</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Customer Service Specialist (Haier)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-specialist-at-haier-4430223135</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IT Director (The Talents Nation)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-director-at-the-talents-nation-4430231610</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Estimation Engineer (TGC Consulting - Middle East)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-estimation-engineer-at-tgc-consulting-middle-east-4432956094</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -13,6 +13,7 @@
     <sheet name="24-06-2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="25-06-2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="26-06-2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="27-06-2026" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9453,4 +9454,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General Accountant and Administrative Assistant (Nomads Roastery)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-accountant-and-administrative-assistant-at-nomads-roastery-4434083300</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Storekeeper – Construction Industry (Ultraction General Contracting)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-%E2%80%93-construction-industry-at-ultraction-general-contracting-4428568848</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4433443732</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Document Controller / Accounts Coordinator (Carbon Asset Management)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-accounts-coordinator-at-carbon-asset-management-4430299828</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Order Processing Assistant (Agthia Group PJSC)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/order-processing-assistant-at-agthia-group-pjsc-4432987154</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Frío Sparkling Water)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-fr%C3%ADo-sparkling-water-4433859662</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Leasing Administration Manager (Al Marwan Real Estate)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/leasing-administration-manager-at-al-marwan-real-estate-4433824696</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Crew Member - Five Guys Dubai (Shamal Holding)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/crew-member-five-guys-dubai-at-shamal-holding-4433429795</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Real Estate Admin cum Accounts Executive (Expert Properties)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/real-estate-admin-cum-accounts-executive-at-expert-properties-4431218639</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SALES ASSOCIATE (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-associate-at-burjline-builders-4433419992</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Head of MOE Subjects (iCademy Middle East)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-moe-subjects-at-icademy-middle-east-4433804602</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Administrative Manager (quickmandi.com)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-manager-at-quickmandi-com-4430662989</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pre Sales Engineer (Technical/Commercial) (BWCN IT Solutions LLC)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pre-sales-engineer-technical-commercial-at-bwcn-it-solutions-llc-4433267780</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr IT Specialist - ERP (Robert Walters)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sr-it-specialist-erp-at-robert-walters-4430288770</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supervisor (Chloé)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-at-chlo%C3%A9-4433273190</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Owner Representative - Hospitality Asset (Confidential)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/owner-representative-hospitality-asset-at-confidential-4432979565</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Executive Assistant - Arabic Speaker (Confidential)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-arabic-speaker-at-confidential-4433599679</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Commercial Sales Support Specialist (Pepperl+Fuchs Group)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/commercial-sales-support-specialist-at-pepperl%2Bfuchs-group-4433890207</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SALES ASSOCIATE (Qureos)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-associate-at-qureos-4430652351</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Purchasing Coordinator (TWU-Center for Women Entrepreneurs)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/purchasing-coordinator-at-twu-center-for-women-entrepreneurs-4433439571</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Car Courier (EMX)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/car-courier-at-emx-4433816829</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Stakeholder Engineer (Khatib &amp; Alami)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-stakeholder-engineer-at-khatib-alami-4433814850</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sales Engineer (Proto21)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-engineer-at-proto21-4430670903</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sales Logistics Specialist (Click Express Transport &amp; Storage LLC)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-logistics-specialist-at-click-express-transport-storage-llc-4433830985</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Project Manager  ( ITMAM) (Abu Dhabi Commercial Bank)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-manager-itmam-at-abu-dhabi-commercial-bank-4433807523</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -14,6 +14,7 @@
     <sheet name="25-06-2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="26-06-2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="27-06-2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="28-06-2026" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10950,4 +10951,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warehouse Assistant (With Driving License) (Great Dubai)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-with-driving-license-at-great-dubai-4434206460</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Coordinator (Unity Star Import and Export FZE LLC)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-coordinator-at-unity-star-import-and-export-fze-llc-4433450988</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Front Office Manager (EDITION)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-edition-4433494656</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Hotel IT &amp; Systems Manager (Real Estate Development)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Picker (talabat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/picker-at-talabat-4346310392</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Personal Assistant to Chief Executive Officer (Abdulla Al-Nuaimi Advocates &amp; Legal Consultants)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-to-chief-executive-officer-at-abdulla-al-nuaimi-advocates-legal-consultants-4433472057</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Citrix Administrator / Consultant (Müller's Solutions)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/citrix-administrator-consultant-at-m%C3%BCller-s-solutions-4434210630</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Assistant Boutique Manager, Abu Dhabi (Jaeger-LeCoultre)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-boutique-manager-abu-dhabi-at-jaeger-lecoultre-4424611118</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Associate - Dubai, UAE (PLL Legal &amp; CBP)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-dubai-uae-at-pll-legal-cbp-4431002089</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SAP SF Time Tracking Consultant (Remote) (Müller's Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sap-sf-time-tracking-consultant-remote-at-m%C3%BCller-s-solutions-4434213385</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Commercial Administrator (Al Awsaf Transport LLC)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Head of Internal Audit (Confidential)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-internal-audit-at-confidential-4434239137</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Project Engineer(DM Licensed) (Iman Developers)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-dm-licensed-at-iman-developers-4434229356</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Public Relations Manager, MENA (Xsolla)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-relations-manager-mena-at-xsolla-4412060041</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Regional Category Buyer (Kerry)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-category-buyer-at-kerry-4412664150</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lead Project Engineer – Customer Project Engineering (GE Vernova)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-project-engineer-%E2%80%93-customer-project-engineering-at-ge-vernova-4424737391</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Flight Engineer (ACJ) | DC Aviation Al Futtaim | Dubai UAE (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/flight-engineer-acj-dc-aviation-al-futtaim-dubai-uae-at-al-futtaim-4415520058</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lead Planning Engineer (Havelock One Interiors)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-planning-engineer-at-havelock-one-interiors-4434267337</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer (Fuse Energy)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/applied-ai-engineer-at-fuse-energy-4434234242</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Recruitment Specialist (Amlak Al Sayyad Real Estate L L C)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/recruitment-specialist-at-amlak-al-sayyad-real-estate-l-l-c-4434226242</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Plumbing Engineering (Intercontinental raz al khaimah)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SAP GRC Consultant (Implementation)-Remote (Müller's Solutions)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sap-grc-consultant-implementation-remote-at-m%C3%BCller-s-solutions-4434207713</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Reverse Logistics - Channel Team Lead, AMET Reverse Logistics (Amazon)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reverse-logistics-channel-team-lead-amet-reverse-logistics-at-amazon-4424766449</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Procurement Manager - Dubai (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-manager-dubai-at-jd-com-4414681663</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Real Estate Agent (Off-Plan Specialist) (MTS Group)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/real-estate-agent-off-plan-specialist-at-mts-group-4430690274</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -15,6 +15,7 @@
     <sheet name="26-06-2026" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="27-06-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="28-06-2026" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="29-06-2026" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12447,4 +12448,1500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Assistant Warehouse Manager  in Construct Domain(must) (TAT IT Technolgies)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-warehouse-manager%C2%A0%C2%A0in-construct-domain-must-at-tat-it-technolgies-4433664473</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Assistant Store Keeper (Innovo Group)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-store-keeper-at-innovo-group-4433669149</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4433646622</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Technical Superintendent (DP World)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-superintendent-at-dp-world-3840232372</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Trivium Group)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-trivium-group-4434299504</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Recovery &amp; Returns Assistant | Retail | IKEA Jebel Ali (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/recovery-returns-assistant-retail-ikea-jebel-ali-at-al-futtaim-4434469255</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Управляющий виллой / Хаусмастер (Confidential Careers)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%D1%83%D0%BF%D1%80%D0%B0%D0%B2%D0%BB%D1%8F%D1%8E%D1%89%D0%B8%D0%B9-%D0%B2%D0%B8%D0%BB%D0%BB%D0%BE%D0%B9-%D1%85%D0%B0%D1%83%D1%81%D0%BC%D0%B0%D1%81%D1%82%D0%B5%D1%80-at-confidential-careers-4434441662</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>⁠⁠Executive Assistant to 2 Co-founders (KIDAN)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%E2%81%A0%E2%81%A0executive-assistant-to-2-co-founders-at-kidan-4434457273</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Tandem Search)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-tandem-search-4431069297</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Front Office Manager (The Dubai EDITION)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-the-dubai-edition-4434435826</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Maintenance Coordinator for Family Residence (Confidential Careers)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-coordinator-for-family-residence-at-confidential-careers-4434448369</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Junior Sales Coordinator - Tendering - Automotive Manufacturing - Dubai (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-sales-coordinator-tendering-automotive-manufacturing-dubai-at-sanvi-engineering-and-business-consulting-solutions-4433641720</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Civil Estimation Engineer (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-estimation-engineer-at-asia-prime-general-contracting-co-l-l-c-4431061232</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Junior Estimation Engineer (Whizz HR)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-estimation-engineer-at-whizz-hr-4434454376</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sales Coordinator - Tendering - Automotive Manufacturing - Dubai Location (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-tendering-automotive-manufacturing-dubai-location-at-sanvi-engineering-and-business-consulting-solutions-4433659114</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Junior Sales Coordinator - Tendering - Automotive Manufacturing - Dubai Location (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-sales-coordinator-tendering-automotive-manufacturing-dubai-location-at-sanvi-engineering-and-business-consulting-solutions-4433635875</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Application Engineer (SKM Air Conditioning LLC)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/application-engineer-at-skm-air-conditioning-llc-4431502272</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Front Office Manager (EDITION)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-edition-4433494656</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Front Office Executive (Dr. Sunny Medical Centre - UAE)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-executive-at-dr-sunny-medical-centre-uae-4434453191</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Accelerec Ltd.)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-engineer-at-accelerec-ltd-4433678192</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FinOps Administrator (LanceSoft Middle East)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/finops-administrator-at-lancesoft-middle-east-4433672274</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Picker (Majid Al Futtaim)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/picker-at-majid-al-futtaim-4433619554</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Officer, Procurement (International Federation of Red Cross and Red Crescent Societies - IFRC)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-officer-procurement-at-international-federation-of-red-cross-and-red-crescent-societies-ifrc-4432577398</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Roads and Infrastructure) (AECOM)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-roads-and-infrastructure-at-aecom-4431410227</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Regulatory - Americas (Huda Beauty)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-regulatory-americas-at-huda-beauty-4408746224</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -16,6 +16,7 @@
     <sheet name="27-06-2026" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="28-06-2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="29-06-2026" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30-06-2026" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1975,6 +1976,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Admin &amp; Operations (Maiz)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-operations-at-maiz-4434905727</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Manager (HRsource)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-hrsource-4431581455</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4434192840</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Office Admin Coordinator (TradeQuo Global)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-admin-coordinator-at-tradequo-global-4434483900</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant Warehouse Manager  in Construct Domain(must) (TAT IT Technolgies)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-warehouse-manager%C2%A0%C2%A0in-construct-domain-must-at-tat-it-technolgies-4433664473</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Confidential)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-confidential-4434962281</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Executive Assistant (La Capitale Real Estate)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-la-capitale-real-estate-4431506328</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Office Management | Executive Support (Yellow Door Energy)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-management-executive-support-at-yellow-door-energy-4434129048</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive Assistant to the Director &amp; Chairman (Unified Credit Solutions)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-the-director-chairman-at-unified-credit-solutions-4431543362</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Executive Assistant -18 months contract (Confidential)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-18-months-contract-at-confidential-4434944577</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Administrative and Procurement/Sales Specialist (Dubai, UAE) (HYPERPC Middle East)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-and-procurement-sales-specialist-dubai-uae-at-hyperpc-middle-east-4431523158</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sales Coordinator (Quantum Edge Distribution)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-at-quantum-edge-distribution-4431513355</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IT Support Engineer / IT Administrator (Xeluxe Fire Safety Consultancy)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-support-engineer-it-administrator-at-xeluxe-fire-safety-consultancy-4431503352</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Freelance / Boutique Team Needed – WhatsApp AI Booking Assistant (Phase 1) (SkyBlueMedia - UAE)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/freelance-boutique-team-needed-%E2%80%93-whatsapp-ai-booking-assistant-phase-1-at-skybluemedia-uae-4434136988</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sales Coordinator - Tendering - Automotive Manufacturing - Dubai (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-tendering-automotive-manufacturing-dubai-at-sanvi-engineering-and-business-consulting-solutions-4434187896</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Freelance Boutique Team Needed WhatsApp AI Booking Assistant Phase 1 (SkyBlueMedia - UAE)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/freelance-boutique-team-needed-whatsapp-ai-booking-assistant-phase-1-at-skybluemedia-uae-4434903672</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Event Coordinator (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/event-coordinator-at-tasc-outsourcing-4434930960</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Procurement Coordinator (EMKAAN Architectural + Engineering Consultancy)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-coordinator-at-emkaan-architectural-%2B-engineering-consultancy-4431578089</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shipping Coordinator (JAMS HR Solutions)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shipping-coordinator-at-jams-hr-solutions-4431088732</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Catering Executive (Sales) (Maiz)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/catering-executive-sales-at-maiz-4434914691</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Retail Sales Specialist (The Laundry Hub)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-sales-specialist-at-the-laundry-hub-4431511484</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Civil / Finishing Engineer (emagine)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-finishing-engineer-at-emagine-4429673023</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Administrator (Jebel Ali) - UAE Nationals only (Emirates Global Aluminium (EGA))</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-administrator-jebel-ali-uae-nationals-only-at-emirates-global-aluminium-ega%E2%80%8B-4431594118</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Contract Engineer (IOTA GROUP)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/contract-engineer-at-iota-group-4434966518</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Customer Support Specialist (Gargash Group)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-support-specialist-at-gargash-group-4424865751</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -17,6 +17,7 @@
     <sheet name="28-06-2026" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="29-06-2026" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="30-06-2026" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="01-07-2026" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3472,6 +3473,1217 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pre-Sales Consultant – Digital Transformation (HLB HAMT - Audit, Tax, Advisory &amp; Consulting)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pre-sales-consultant-%E2%80%93-digital-transformation-at-hlb-hamt-audit-tax-advisory-consulting-4432348717</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IT Support Specialist (Real Estate Industry) (H&amp;R Real Estate Brokerage | Arm of Amer Al Ghurair  Group)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-support-specialist-real-estate-industry-at-h-r-real-estate-brokerage-arm-of-amer-al-ghurair-group-4432324910</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arabia Customer Service Specialist (Unilever)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/arabia-customer-service-specialist-at-unilever-4434332322</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Whizz HR)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-whizz-hr-4435123070</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Officer | Training, Compliance &amp; Process | E-commerce Operations (UnionCoop)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-officer-training-compliance-process-e-commerce-operations-at-unioncoop-4434194991</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Public Sector Specialist - Senior Manager (Arabic Speaker) (Auxo Talent)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-sector-specialist-senior-manager-arabic-speaker-at-auxo-talent-4432331336</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Civil Engineer (Overhead Line) (Power Tech Development W.L.L)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-engineer-overhead-line-at-power-tech-development-w-l-l-4432335200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Receptionist cum Admin (Genius HRTech Services L.L.C - FZ - Dubai)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receptionist-cum-admin-at-genius-hrtech-services-l-l-c-fz-dubai-4434143409</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Strategic Account Manager, Travel Seller (TPConnects Technologies)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-strategic-account-manager-travel-seller-at-tpconnects-technologies-4431900751</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Luxury Private Client Consultant (DXBA)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/luxury-private-client-consultant-at-dxba-4432331274</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EEMC Technical Shop Support Officer (Emirates)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/eemc-technical-shop-support-officer-at-emirates-4432307898</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Associate University Librarian: Public Services | University Library (American University of Sharjah)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-university-librarian-public-services-university-library-at-american-university-of-sharjah-4416232031</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Supervisor Safety (UAE National) (Emirates Global Aluminium (EGA))</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-safety-uae-national-at-emirates-global-aluminium-ega%E2%80%8B-4432315532</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Head of Engineering (UMATR)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-engineering-at-umatr-4431229028</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Site Manager (Al Abbar Group)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-manager-at-al-abbar-group-4431936178</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Office Manager &amp; Executive Assistant (Guerlain)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-executive-assistant-at-guerlain-4431909740</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retail Store Planner - Mall of the Emirates (Hermès)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-store-planner-mall-of-the-emirates-at-herm%C3%A8s-4394426757</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Safety Manager | Dubai, UAE (Moove)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/safety-manager-dubai-uae-at-moove-4433243609</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Platform Lead (Tata Consultancy Services)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ai-platform-lead-at-tata-consultancy-services-4434333288</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Electronics Sourcing Executive (Al Waha For Cars)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/electronics-sourcing-executive-at-al-waha-for-cars-4432327979</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -18,6 +18,7 @@
     <sheet name="29-06-2026" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="30-06-2026" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="01-07-2026" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="02-07-2026" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4684,6 +4685,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Store Keeper (Sobha Constructions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-keeper-at-sobha-constructions-4434673238</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SAP Positions (TATWEER MIDDLE EAST AND AFRICA L.L.C)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sap-positions-at-tatweer-middle-east-and-africa-l-l-c-4436195807</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SENIOR REAL ESTATE ADMINISTRATOR (Zenith Technologies)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-real-estate-administrator-at-zenith-technologies-4432743835</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Document Controller / Asset Management Coordinator (Golden Tower Metal Industries LLC)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-asset-management-coordinator-at-golden-tower-metal-industries-llc-4435560842</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Admin cum Accountant (KAJ Properties)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-cum-accountant-at-kaj-properties-4432761697</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Admin &amp; Collection Assistant (H&amp;R Real Estate Brokerage | Arm of Amer Al Ghurair  Group)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-collection-assistant-at-h-r-real-estate-brokerage-arm-of-amer-al-ghurair-group-4432381200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Operations &amp; Administration Coordinator (CXC Upstream Ltd)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-administration-coordinator-at-cxc-upstream-ltd-4435812314</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant to C Suite (Confidential)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-c-suite-at-confidential-4432712430</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Administrator (XSpot Wealth)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-administrator-at-xspot-wealth-4435812023</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Assistant General Manager - Accounts (Sobha Constructions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-general-manager-accounts-at-sobha-constructions-4426285948</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Project Manager (Enerflex Ltd.)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-manager-at-enerflex-ltd-4413339126</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Document Controller (International Engineering Consultancy)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Oldtimer Middle East)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-oldtimer-middle-east-4432387654</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cost Clerk | Al-Futtaim Motors | Toyota (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-clerk-al-futtaim-motors-toyota-at-al-futtaim-4435541880</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Engineer-Roads Maintenance (UAE National) (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-engineer-roads-maintenance-uae-national-at-roads-and-transport-authority-4432704157</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Commissioning Manager (International Engineering Consultancy)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Site Manager - Data Center (JCA Associates)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-manager-data-center-at-jca-associates-4432765167</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>行政专员 (Hikvision MEA)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%E8%A1%8C%E6%94%BF%E4%B8%93%E5%91%98-at-hikvision-mea-4432745477</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Materials Engineer (International Engineering Consultancy)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Project Engineer – WMS Super User (CEVA Logistics)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-%E2%80%93-wms-super-user-at-ceva-logistics-4432751395</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Services Sales Manager, Middle East (Nutanix)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/services-sales-manager-middle-east-at-nutanix-4434655513</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Bid &amp; Project Coordinator (White Space Recruitment)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/bid-project-coordinator-at-white-space-recruitment-4436314018</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POS Sales Acquisition Team Lead - UAE (Paymob)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pos-sales-acquisition-team-lead-uae-at-paymob-4435812766</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ops Admin Coordinator (DHL Supply Chain)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ops-admin-coordinator-at-dhl-supply-chain-4435826020</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Resident Engineer (Eiger Marvel Consultants)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-resident-engineer-at-eiger-marvel-consultants-4432747400</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -19,6 +19,7 @@
     <sheet name="30-06-2026" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="01-07-2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="02-07-2026" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="03-07-2026" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6181,6 +6182,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Camp Manager (Confidential)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/camp-manager-at-confidential-4436497070</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shift Manager - Base Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shift-manager-base-maintenance-at-air-arabia-4436341858</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dubai Admin Lead (Bybit)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dubai-admin-lead-at-bybit-4435213035</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Center Facility Manager-Dubai (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-center-facility-manager-dubai-at-alibaba-cloud-4423621257</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Construction Document Controller, EMEA Pre-Construction (Amazon Web Services (AWS))</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-document-controller-emea-pre-construction-at-amazon-web-services-aws-4436386396</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vice President Operations &amp; Maintenance Power (EtihadWE)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/vice-president-operations-maintenance-power-at-etihadwe-4432771396</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mobile Engineering Manager (talabat)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mobile-engineering-manager-at-talabat-4433160168</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Office Manager - UAE National (Ministry of Community Empowerment)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-uae-national-at-ministry-of-community-empowerment-4436478470</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>QHSE Supervisor (Mezzan Foods)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qhse-supervisor-at-mezzan-foods-4433151942</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Logistics Administrator(JAFZA) (JAMS HR Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-administrator-jafza-at-jams-hr-solutions-4433148775</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Project Controls Admin (UAE National) (Wood)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-controls-admin-uae-national-at-wood-4436704343</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technical Account Management-Dubai (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-account-management-dubai-at-alibaba-cloud-4432770249</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EFS Assistant (Emirates Flight Catering)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/efs-assistant-at-emirates-flight-catering-4436481535</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Manager, Food Engineering (Emirates Flight Catering)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-food-engineering-at-emirates-flight-catering-4433157604</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Team Leader – Site Operations (LYNX INTERNATIONAL)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-%E2%80%93-site-operations-at-lynx-international-4433121435</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Installation Manager (Al Abbar Group)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/installation-manager-at-al-abbar-group-4433170045</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Head of Corporate Governance (Aramex)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-corporate-governance-at-aramex-4436303855</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Engineering Supervisor - Marriott Executive Apartments Sheikh Zayed Road (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-supervisor-marriott-executive-apartments-sheikh-zayed-road-at-marriott-executive-apartments-4435253986</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Program Manager, Amazon Now, Quick Commerce (Amazon)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/program-manager-amazon-now-quick-commerce-at-amazon-4423133435</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>O&amp;M Engineer - Water &amp; Wastewater treatment (Net2Source (N2S))</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/o-m-engineer-water-wastewater-treatment-at-net2source-n2s-4436487530</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WHS Safety Coordinator - Accommodation Program, WHS - Vendor Accommodation Audit Program (Amazon)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/whs-safety-coordinator-accommodation-program-whs-vendor-accommodation-audit-program-at-amazon-4436446398</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Regulatory Compliance Manager - Compliance (United Arab Bank)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regulatory-compliance-manager-compliance-at-united-arab-bank-4433172020</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Relationship Manager (CXC Upstream Ltd)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relationship-manager-at-cxc-upstream-ltd-4436409597</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Storekeeper (Main Contractor Backgroud) (The Orchard Place)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-main-contractor-backgroud-at-the-orchard-place-4436334373</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Project Technical Manager (Ignite Search and Selection)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-technical-manager-at-ignite-search-and-selection-4433167089</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -20,6 +20,7 @@
     <sheet name="01-07-2026" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="02-07-2026" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="03-07-2026" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="04-07-2026" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7678,6 +7679,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Storekeeper (Zahr Freighters)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-at-zahr-freighters-4436770457</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HR &amp; Admin Executive (Dicetek LLC)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-admin-executive-at-dicetek-llc-4436796931</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Store keeper – Heavy Machinery Spare Parts (Al Marwan Group)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-keeper-%E2%80%93-heavy-machinery-spare-parts-at-al-marwan-group-4435483320</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4435765170</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Administration Specialist (Knight Frank MENA)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-specialist-at-knight-frank-mena-4435448517</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CEO Assistant - Food &amp; Beverage (Al Salah Holding)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ceo-assistant-food-beverage-at-al-salah-holding-4433178793</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Administrative Specialist-Dubai(A252680) (PayerMax)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-administrative-specialist-dubai-a252680-at-payermax-4436701543</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Front Office Manager (The Dubai EDITION)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-the-dubai-edition-4436918915</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Office Coordinator (Zokolat Craft Chocolates)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-coordinator-at-zokolat-craft-chocolates-4431919307</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VIP Aftersales Specialist (Remote) (HomeKode)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/vip-aftersales-specialist-remote-at-homekode-4433195396</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Asset &amp; Maintenance Management System Manager (AMMS) (Keolis.MHI)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/asset-maintenance-management-system-manager-amms-at-keolis-mhi-4436741198</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Email &amp; Domain Security Administrator (Tebesty General Trading)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/email-domain-security-administrator-at-tebesty-general-trading-4433173973</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Inventory Manager (Pattern)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-manager-at-pattern-4436730900</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Whizz HR)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-whizz-hr-4436709419</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Principal Package Management Spec (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/principal-package-management-spec-at-mcdermott-international-ltd-4418003581</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Assistant Personnel Manager (Al Salah Holding)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-personnel-manager-at-al-salah-holding-4433733449</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shipping Operations Executive (Gunvor Group)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shipping-operations-executive-at-gunvor-group-4433712437</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Line Supervisor (Emirates Flight Catering)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/line-supervisor-at-emirates-flight-catering-4436717231</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Parts Purchaser officer (Ember Automotive)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/parts-purchaser-officer-at-ember-automotive-4433177173</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Operations/ Accounts Executive | Retail | M&amp;S | UAE (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-accounts-executive-retail-m-s-uae-at-al-futtaim-4436712409</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Joinery Supervisor (VBF Group)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/joinery-supervisor-at-vbf-group-4433734406</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Processing Manager (Astons. Investment Migration Firm)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/processing-manager-at-astons-investment-migration-firm-4436733594</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Reservation, Ticketing &amp; Holiday Consultant (Arabic Speaking) (Diala Travel &amp; Tourism)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reservation-ticketing-holiday-consultant-arabic-speaking-at-diala-travel-tourism-4433164809</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Network Planning Support Officer (Sharjah, UAE) (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/network-planning-support-officer-sharjah-uae-at-air-arabia-4436733832</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sales Assistant - Dubai (Golden Goose)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-assistant-dubai-at-golden-goose-4427965174</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -21,6 +21,7 @@
     <sheet name="02-07-2026" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="03-07-2026" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="04-07-2026" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="05-07-2026" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9175,6 +9176,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Head of Operations (Elite HR Consultancy)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-operations-at-elite-hr-consultancy-4436037197</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EHS Engineer (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ehs-engineer-at-larsen-toubro-4400535073</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Industrial Engineer (SKM Air Conditioning LLC)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/industrial-engineer-at-skm-air-conditioning-llc-4433741832</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Gulf Orchid Perfume Manufacturing)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-gulf-orchid-perfume-manufacturing-4433732934</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant Service Manager (Printing machinery supplier) (NADIA)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-service-manager-printing-machinery-supplier-at-nadia-4433738522</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Procurement Supervisor (Cabin &amp; IFE) - Emiratisation (Emirates)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-supervisor-cabin-ife-emiratisation-at-emirates-4433782289</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REGIONAL PRODUCT SUPPORT SPECIALIST, MIDDLE EAST &amp; TURKEY (Dynapac France SAS)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-product-support-specialist-middle-east-turkey-at-dynapac-france-sas-4433766100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant &amp; Operations Coordinator (Mignon Design Build)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-operations-coordinator-at-mignon-design-build-4433777797</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager -Manufacturing Industry (Taif Al Emarat | طيف الإمارات)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-manager-manufacturing-industry-at-taif-al-emarat-%D8%B7%D9%8A%D9%81-%D8%A7%D9%84%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA-4433754266</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>All jobs (Atovee Steel Constructions Contracting LLC)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/all-jobs-at-atovee-steel-constructions-contracting-llc-4433787403</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cost Control Engineer | High Rise Building (ABU ALNAGA CONTRACTING)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-control-engineer-high-rise-building-at-abu-alnaga-contracting-4433735712</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Account Manager-GCC (Brand Aid Marketing Solutions)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/account-manager-gcc-at-brand-aid-marketing-solutions-4433741703</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist (TechNest support center FZ L.L.C)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/talent-acquisition-specialist-at-technest-support-center-fz-l-l-c-4433740699</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Jordan) (Palo Alto Networks)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/systems-engineer-jordan-at-palo-alto-networks-4406789062</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Online Merchandiser | Retail | M&amp;S | UAE (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/online-merchandiser-retail-m-s-uae-at-al-futtaim-4428108770</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Full-stack Engineer (Flatgigs)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-full-stack-engineer-at-flatgigs-4436935710</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bids &amp; Portals Coordinator - Arabic Speaker (Kroll)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/bids-portals-coordinator-arabic-speaker-at-kroll-4424898687</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3 ton pickup driver for event and wedding company (Liali Events Organizing | Design | Production | Wedding Planning  | Corporate Events | Coordination)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/3-ton-pickup-driver-for-event-and-wedding-company-at-liali-events-organizing-design-production-wedding-planning-corporate-events-coordination-4433781337</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Assistant Brand Manager - Perfume Manufacturing Industry (Taif Al Emarat | طيف الإمارات)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-brand-manager-perfume-manufacturing-industry-at-taif-al-emarat-%D8%B7%D9%8A%D9%81-%D8%A7%D9%84%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA-4433756156</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Customer Service Specialist (Hyva)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-specialist-at-hyva-4426947811</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Export Sales Executive – Perfume Industry (Gulf Orchid Perfume Manufacturing)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/export-sales-executive-%E2%80%93-perfume-industry-at-gulf-orchid-perfume-manufacturing-4433754040</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CP - Civil Transmission Line | UAE (Hudson IT and Manpower)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cp-civil-transmission-line-uae-at-hudson-it-and-manpower-4436931981</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Communication and Content Specialist - Dubai, UAE (Siemens)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-communication-and-content-specialist-dubai-uae-at-siemens-4435797616</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Job Description – QA Engineer (Manual &amp; Automation Testing) (Unicorn Lab)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/job-description-%E2%80%93-qa-engineer-manual-automation-testing-at-unicorn-lab-4433735887</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Maintenance-Technician I (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-technician-i-at-marriott-executive-apartments-4436011217</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -22,6 +22,7 @@
     <sheet name="03-07-2026" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="04-07-2026" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="05-07-2026" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="06-07-2026" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10672,6 +10673,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Office Manager (Technology Startup) (HRsource)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-technology-startup-at-hrsource-4433939183</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Administrator (Citizenship &amp; Co)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrator-at-citizenship-co-4433796591</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Accommodation Manager (Confidential)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/accommodation-manager-at-confidential-4437145659</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Executive Assistant[C-Suite] -18 months contract (Confidential)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-c-suite-18-months-contract-at-confidential-4437159134</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Luxliving Real Estate)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-luxliving-real-estate-4433922362</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Receiptionist / front desk assistant (Yalladuka - Buy or Sell anything in UAE)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receiptionist-front-desk-assistant-at-yalladuka-buy-or-sell-anything-in-uae-4436991664</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hiring Receiptionist (Yalladuka - Buy or Sell anything in UAE)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hiring-receiptionist-at-yalladuka-buy-or-sell-anything-in-uae-4436983946</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Richemont)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-richemont-4436041579</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Collection Officer (Cartrack Middle East)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/collection-officer-at-cartrack-middle-east-4433945076</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Accounts Manager (ACCEL HUMAN RESOURCE CONSULTANTS)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/accounts-manager-at-accel-human-resource-consultants-4433933148</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Resident Engineer (AECOM)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-resident-engineer-at-aecom-4436076627</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Quality Control Engineer (Caliberly® -  Recruitment Agency)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/quality-control-engineer-at-caliberly%C2%AE-recruitment-agency-4437150614</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Research And Development Manager (Americana Restaurants)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/research-and-development-manager-at-americana-restaurants-4433905844</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Office Administration &amp; Premises Management (The Impact Foundation)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administration-premises-management-at-the-impact-foundation-4437141945</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chief Specialist Customer Experience (Arabic Speakers) (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-specialist-customer-experience-arabic-speakers-at-roads-and-transport-authority-4433926374</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Procurement Officer (Lagash Group of Companies)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-officer-at-lagash-group-of-companies-4433782973</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Public Relations Officer(PRO) - SAIF ZONE Experience Required (Millennium Fashions Industries Ltd)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-relations-officer-pro-saif-zone-experience-required-at-millennium-fashions-industries-ltd-4433749466</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Director of Engineering (Rebel Recruiters)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/director-of-engineering-at-rebel-recruiters-4433935502</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT Specialist - Cloud Administrative (Vanderlande)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-specialist-cloud-administrative-at-vanderlande-4407694371</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Coordinator Sales - Local Shops - UAE National (talabat)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/coordinator-sales-local-shops-uae-national-at-talabat-4436081251</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Boutique Project Trainee (Intern) (AMOUAGE)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/boutique-project-trainee-intern-at-amouage-4433928737</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr. Supervisor - Equip. Maint. (Sundus)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sr-supervisor-equip-maint-at-sundus-4437157197</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Emirati Future Talent Pool (talabat)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/emirati-future-talent-pool-at-talabat-4436083272</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineer - Equipment Commis. (Sundus)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineer-equipment-commis-at-sundus-4437139529</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sales Associate (Majid Al Futtaim)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-associate-at-majid-al-futtaim-4433927701</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -23,6 +23,7 @@
     <sheet name="04-07-2026" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="05-07-2026" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="06-07-2026" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="07-07-2026" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12169,6 +12170,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Assistant General Manager - Accounts (Sobha Constructions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-general-manager-accounts-at-sobha-constructions-4426285948</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Office Manager (Crone Corkill)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-crone-corkill-4433955840</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Metso)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-metso-4436215827</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Office Manager (Technology Startup) (HRsource)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-technology-startup-at-hrsource-4433939183</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant Accounts Receivable - Head Office (Fundamental Hospitality)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-accounts-receivable-head-office-at-fundamental-hospitality-4437168658</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Storekeeper / Receiving Clerk (NH Collection Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-receiving-clerk-at-nh-collection-hotels-resorts-4433978619</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Storekeeper / Receiving Clerk (Minor Hotels)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-receiving-clerk-at-minor-hotels-4437405600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4436526037</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Payroll Specialist (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/payroll-specialist-at-air-arabia-4437186807</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Buccellati)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-buccellati-4417860099</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Warehouse Assistant Supervisor (Al Khayyat Investments (AKI))</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-supervisor-at-al-khayyat-investments-aki-4434503386</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Document Controller (AECOM)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-aecom-4436537151</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Agile Consultants)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-agile-consultants-4437731203</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Client Accounting Supervisor (Talent Higher)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/client-accounting-supervisor-at-talent-higher-4436083648</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technical Support Specialist (Beijing Foreign Enterprise Management Consultants Co.,Ltd.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-specialist-at-beijing-foreign-enterprise-management-consultants-co-ltd-4437754075</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Sales Engineer (Technical/Commercial) (BWCN IT Solutions LLC)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pre-sales-engineer-technical-commercial-at-bwcn-it-solutions-llc-4436518529</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Elite Assistant Relationship Manager (Arab Bank)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/elite-assistant-relationship-manager-at-arab-bank-4433948390</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Cargo Coordinator (Apollo Freight Solutions Group)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-cargo-coordinator-at-apollo-freight-solutions-group-4433935842</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Floor Manager (The Arts Club)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/floor-manager-at-the-arts-club-4437167634</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HR Specialist | Office Admin (BTSE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-specialist-office-admin-at-btse-4437740632</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Active Directory, M365 &amp; Windows Server Administrator (LanceSoft Middle East)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/active-directory-m365-windows-server-administrator-at-lancesoft-middle-east-4436535309</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Procurement Engineer - HVAC (FJ Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-engineer-hvac-at-fj-group-4437178485</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Site Engineer (ACCEL HUMAN RESOURCE CONSULTANTS)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-engineer-at-accel-human-resource-consultants-4434517511</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Head of Communications, MENA (TikTok)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-communications-mena-at-tiktok-4436227933</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer (CEO) – Shipping &amp; Logistics (Confidential)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-executive-officer-ceo-%E2%80%93-shipping-logistics-at-confidential-4437741617</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -24,6 +24,7 @@
     <sheet name="05-07-2026" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="06-07-2026" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="07-07-2026" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="08-07-2026" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13666,6 +13667,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>warehouse incharge (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-incharge-at-burjline-builders-4436876746</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Supermarket &amp; Hypermarket Frontline Position | Everyday Goods - Retail | UAE (GMG)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supermarket-hypermarket-frontline-position-everyday-goods-retail-uae-at-gmg-4436590818</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Leasing Administrator - UAEN (Gargash Group)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/leasing-administrator-uaen-at-gargash-group-4436899895</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Team Assistant- IMEA Leadership Team (Brink’s Inc)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-assistant-imea-leadership-team-at-brink%E2%80%99s-inc-4437753969</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Store Keeper (Visioneers)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-keeper-at-visioneers-4436559260</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4437024207</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sales Coordinator (Confidential)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-at-confidential-4434839095</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>warehouse incharge (Qureos)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-incharge-at-qureos-4434584819</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Kingston Stanley)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-kingston-stanley-4436541494</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4437008637</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopping Experience Assistant - Cashier | Retail | IKEA Jebel Ali (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shopping-experience-assistant-cashier-retail-ikea-jebel-ali-at-al-futtaim-4437828736</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chair side dental assistant 1 (Dubai Careers - A Smart Dubai Initiative)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chair-side-dental-assistant-1-at-dubai-careers-a-smart-dubai-initiative-4437781030</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Client Invoicing) (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-client-invoicing-at-larsen-toubro-4410582243</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior System Engineer (Scale Up Construction Consulting)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-system-engineer-at-scale-up-construction-consulting-4438178621</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Information Technology Support Specialist (JOLAHA - THE WEAVER)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-technology-support-specialist-at-jolaha-the-weaver-4434814841</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Procurement Assistant (Khanati Group)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-assistant-at-khanati-group-4437774804</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Document Controller (AECOM)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-aecom-4436537151</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Civil Estimation Engineer (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-estimation-engineer-at-asia-prime-general-contracting-co-l-l-c-4434822684</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Team Leader (Boo Boo Laand)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-boo-boo-laand-4434817740</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Assistant Operations Manager (Calo Inc.)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-operations-manager-at-calo-inc-4436838622</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Material Inspector (Zutari)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/material-inspector-at-zutari-4437837663</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Government Affairs Executive (Ellington Properties Development LLC)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/government-affairs-executive-at-ellington-properties-development-llc-4437836252</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Customer Success Specialist - Freight (Aramex)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-success-specialist-freight-at-aramex-4437798080</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineer-Planning (AECOM)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineer-planning-at-aecom-4436250485</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mall Manager (TML Recruitment)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mall-manager-at-tml-recruitment-4436570664</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -25,6 +25,7 @@
     <sheet name="06-07-2026" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="07-07-2026" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="08-07-2026" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="09-07-2026" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15163,6 +15164,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Administrative Manager (GFS  Developments)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-manager-at-gfs-developments-4435655606</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Residential Sales and Administration Coordinator (Aman)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/residential-sales-and-administration-coordinator-at-aman-4438607426</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Executive Assistant - Hospitality (edari)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-hospitality-at-edari-4438222646</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Office management supervisor (ALDAR)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-management-supervisor-at-aldar-4437335973</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Administrative Executive (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-executive-at-al-futtaim-4438204318</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4437347923</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Office Administrator, UAE(A227705) (Xiaomi Technology)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-uae-a227705-at-xiaomi-technology-4437028595</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Administrative Services Section Manager (Dubai Careers - A Smart Dubai Initiative)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-services-section-manager-at-dubai-careers-a-smart-dubai-initiative-4438196612</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Back Office Manager (SeQure Technologies)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/back-office-manager-at-sequre-technologies-4438207227</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Claims Officer (Lockton)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-claims-officer-at-lockton-4438587956</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Technical and Service support Eng (Bosch Home Comfort Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-and-service-support-eng-at-bosch-home-comfort-group-4435658507</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Operations Technology (DWC, Dubai) (FedEx)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-engineer-operations-technology-dwc-dubai-at-fedex-4438578771</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet Manager (AJI Rentals)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/fleet-manager-at-aji-rentals-4434841973</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Head of Greenfield Joinery Development (Ambitek UAE)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-greenfield-joinery-development-at-ambitek-uae-4430450159</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hook Up Specialist- Mechanical (Subsea7)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hook-up-specialist-mechanical-at-subsea7-4410015767</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Linux Administrator (Tata Consultancy Services)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/linux-administrator-at-tata-consultancy-services-4428037471</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Network Engineer (Crescent Petroleum)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/network-engineer-at-crescent-petroleum-4437334722</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Housekeeping Manager | UAE (Caviar Careers)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/housekeeping-manager-uae-at-caviar-careers-4438270678</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chaingers: Operations Leadership Program (Henkel)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chaingers-operations-leadership-program-at-henkel-4402059494</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SENIOR PROJECT ENGINEER (DP World)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-project-engineer-at-dp-world-4438201345</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cost Control Engineer (Sky International Technical Works L.L.C)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-control-engineer-at-sky-international-technical-works-l-l-c-4435633569</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Demand and Supply Planner (Jotun Middle East, India and Africa (MEIA))</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/demand-and-supply-planner-at-jotun-middle-east-india-and-africa-meia-4437360657</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Customer Experience Assistant Manager (Unilever)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-experience-assistant-manager-at-unilever-4437322061</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Maintenance Manager (FL Technics)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-manager-at-fl-technics-4434856177</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Assistant Storekeeper (The Talents Nation)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-storekeeper-at-the-talents-nation-4435635727</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -26,6 +26,7 @@
     <sheet name="07-07-2026" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="08-07-2026" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="09-07-2026" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="10-07-2026" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18158,6 +18159,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Junior Production Supervisor (Hempel A/S)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-production-supervisor-at-hempel-a-s-4427348960</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Camp Boss (Confidential)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/camp-boss-at-confidential-4437965185</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Executive Handover and DLP (edari)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-handover-and-dlp-at-edari-4438627375</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Resident Engineer (Raqmiyat)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/resident-engineer-at-raqmiyat-4435960964</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Manager - Components Management (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-components-management-at-air-arabia-4430461843</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Office and Operations Manager (GTMfund)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-and-operations-manager-at-gtmfund-4438651336</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Team Leader (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-jd-com-4438648803</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cost Engineer (Lamprell)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-engineer-at-lamprell-4435972225</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Bartawi General Contracting)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-bartawi-general-contracting-4435942754</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Warehouse Supervisor (Deluxe Holiday Homes)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-supervisor-at-deluxe-holiday-homes-4439035274</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Planner - Road or Infrastructure Only (No Buildings) (Al Marwan Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planner-road-or-infrastructure-only-no-buildings-at-al-marwan-group-4437587708</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coordinator - ADP data entry (Dubai Airports)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/coordinator-adp-data-entry-at-dubai-airports-4438643506</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Call Center Supervisor (Eve Medical Center LLC (Dubai,Ajman - Sharjah - RAK - Fujairah - Oman ))</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Production Engineer (paints &amp; chemical company)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OPERATIONS SUPERVISOR (DP World)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-supervisor-at-dp-world-4438625326</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Purchase Executive (Automotive) (Thrifty Car Rental UAE)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/purchase-executive-automotive-at-thrifty-car-rental-uae-4435661707</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technical Manager (Joinery/Fit-Out) (Juma Al Majid Holding Group L.L.C)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-manager-joinery-fit-out-at-juma-al-majid-holding-group-l-l-c-4435902543</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mgr-Engineering (St. Regis Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mgr-engineering-at-st-regis-hotels-resorts-4437919382</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Nursery Manager (Head of Early Years)-Sharjah (Jumeirah International Nurseries)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/nursery-manager-head-of-early-years-sharjah-at-jumeirah-international-nurseries-4438611483</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warehouse Team Lead – Automotive Spare Parts (PLUM JOBS)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-team-lead-%E2%80%93-automotive-spare-parts-at-plum-jobs-4435949079</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Procurement Engineer (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-engineer-at-cscec-middle-east-4435660921</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Public Relations Officer (PRO) (Palma Beach Resort and Spa)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-relations-officer-pro-at-palma-beach-resort-and-spa-4435953537</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Site Supersivor - Interior Design (Tint Tone &amp; Shade)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-supersivor-interior-design-at-tint-tone-shade-4438634123</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Category Management Executive (Careem)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/category-management-executive-at-careem-4435431920</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SAP Project Manager (Landmark International Auto Spare Parts Trading LLC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sap-project-manager-at-landmark-international-auto-spare-parts-trading-llc-4435957268</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -27,6 +27,7 @@
     <sheet name="08-07-2026" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="09-07-2026" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="10-07-2026" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="11-07-2026" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19655,6 +19656,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MFP &amp; Print Solutions Team (Multiple Openings) (Epic Solutions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mfp-print-solutions-team-multiple-openings-at-epic-solutions-4436651944</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Spare Parts Officer (KONE)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/spare-parts-officer-at-kone-4430953683</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Assistant Manager -Logistics (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-logistics-at-larsen-toubro-4439057807</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Resident Engineer (Raqmiyat)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/resident-engineer-at-raqmiyat-4435960964</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Lamprell)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-lamprell-4435971295</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cost Engineer (Lamprell)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-engineer-at-lamprell-4435972225</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Lead Design - WTG (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-design-wtg-at-larsen-toubro-4364671714</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Warehouse Supervisor (Deluxe Holiday Homes)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-supervisor-at-deluxe-holiday-homes-4439035274</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Store Manager (MINIMALIST)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-at-minimalist-4435994288</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campus Maintenance Manager (Eaton)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/campus-maintenance-manager-at-eaton-4435986680</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finance Assistant (The Arab Lens)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/finance-assistant-at-the-arab-lens-4438314443</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ID Manager (Khatib &amp; Alami)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/id-manager-at-khatib-alami-4439036642</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Asst. Construction Manager - Civil (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/asst-construction-manager-civil-at-larsen-toubro-4390387169</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Customer Service Team Lead (Innovations Global)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-team-lead-at-innovations-global-4437995712</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Civil Estimation Engineer (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-estimation-engineer-at-asia-prime-general-contracting-co-l-l-c-4435983134</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Receptionist (CBRE Excellerate)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receptionist-at-cbre-excellerate-4439308973</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sales Support Officer - UAEN (United Diesel)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-support-officer-uaen-at-united-diesel-4439038044</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Clinic Administrator (Camali Clinic)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/clinic-administrator-at-camali-clinic-4435990198</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Technical Engineer (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-engineer-at-talentmate-4439517319</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Oman) (Palo Alto Networks)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/systems-engineer-oman-at-palo-alto-networks-4435988740</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Resident Engineer (Khatib &amp; Alami)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-resident-engineer-at-khatib-alami-4439030783</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sales &amp; Client Operations Coordinator (Petra Brands)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-client-operations-coordinator-at-petra-brands-4439079385</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sales Manager / Sales Engineer (TAT IT Technolgies)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-manager-sales-engineer-at-tat-it-technolgies-4438908597</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Product Support Technician (Konecranes)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/product-support-technician-at-konecranes-4436602058</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IT Systems Specialist (ERP Mircosoft Dynamics|AI Digital transformation ) (Genius HRTech Services L.L.C - FZ - Dubai)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-systems-specialist-erp-mircosoft-dynamics-ai-digital-transformation-at-genius-hrtech-services-l-l-c-fz-dubai-4437990247</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -28,6 +28,7 @@
     <sheet name="09-07-2026" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="10-07-2026" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="11-07-2026" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="12-07-2026" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21152,6 +21153,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workshop Supervisor (BlueMoon Auto Maintenance Workshop)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-supervisor-at-bluemoon-auto-maintenance-workshop-4435943501</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Construction Tech (Fab) (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-tech-fab-at-mcdermott-international-ltd-4439541461</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IT Administrator (Job Sathi)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-administrator-at-job-sathi-4438938567</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HR &amp; Admin Supervisor (The Talents Nation)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-admin-supervisor-at-the-talents-nation-4436675232</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Compliance Applications Support Specialist (Raqmiyat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/compliance-applications-support-specialist-at-raqmiyat-4437207505</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Relocate to Dubai | Luxury Hospitality Careers | General Manager |  Dubai, UAE (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relocate-to-dubai-luxury-hospitality-careers-general-manager-dubai-uae-at-ali-professional-4439558165</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Email &amp; Domain Security Administrator (Tebesty General Trading)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/email-domain-security-administrator-at-tebesty-general-trading-4433173973</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Head of Data Management (Emirati) (Talents Tide)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-data-management-emirati-at-talents-tide-4438933351</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Design Lead - Substation (Civil &amp; Structural) (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/design-lead-substation-civil-structural-at-larsen-toubro-4402975572</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Relocate to Dubai | Luxury Hospitality Careers | General Manager | Nightlife Venue | Dubai (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relocate-to-dubai-luxury-hospitality-careers-general-manager-nightlife-venue-dubai-at-ali-professional-4439542686</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Food Quality Specialist (Calo Inc.)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/food-quality-specialist-at-calo-inc-4438964389</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer (BD SELECT)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-executive-officer-at-bd-select-4436668989</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineering Manager (Dyson)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-software-engineering-manager-at-dyson-4380785148</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Quality Assurance Manager (SAIKOR SECURITY TRAINING AND SERVICES PRIVATE LIMITED)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/quality-assurance-manager-at-saikor-security-training-and-services-private-limited-4438969976</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Document Controller - (VT Design Consultancy) (VTI GLOBAL Vertical Transportation Systems Consultant LLC)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-document-controller-vt-design-consultancy-at-vti-global-vertical-transportation-systems-consultant-llc-4436669690</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SOC Operations Specialist (spiderSilk)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/soc-operations-specialist-at-spidersilk-4409704169</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (emaratechDubai)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-data-engineer-at-emaratechdubai-4439589375</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer (Adecco)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-engineer-at-adecco-4438577758</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Office Administrator | Dubai (Seaborne Shipbrokers S.A.)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-dubai-at-seaborne-shipbrokers-s-a-4439574233</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Store Manager OVS (Dubai Mall) (OVS S.p.A.)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-ovs-dubai-mall-at-ovs-s-p-a-4409291519</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fresh Truffle &amp; Premium Ingredients Assistant (Albadoris)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/fresh-truffle-premium-ingredients-assistant-at-albadoris-4436660873</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Deputy Chief Flight Instructor (flydubai)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/deputy-chief-flight-instructor-at-flydubai-4439587417</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Safety / EHS Engineer – Overhead Transmission Line (OHTL) &amp; Substation – UAE (L1) (Hudson IT and Manpower)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/safety-ehs-engineer-%E2%80%93-overhead-transmission-line-ohtl-substation-%E2%80%93-uae-l1-at-hudson-it-and-manpower-4439546429</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>General Cashier Cum Paymaster (Accor)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-cashier-cum-paymaster-at-accor-4438966288</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Quality Assurance Manager (SAIKOR SECURITY TRAINING AND SERVICES PRIVATE LIMITED)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/quality-assurance-manager-at-saikor-security-training-and-services-private-limited-4438983192</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -29,6 +29,7 @@
     <sheet name="10-07-2026" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="11-07-2026" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="12-07-2026" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="13-07-2026" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22649,6 +22650,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Warehouse Assistant (IRE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-at-ire-4439781679</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sales Administrator / BD Coordinator (eMagine Solutions)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-administrator-bd-coordinator-at-emagine-solutions-4439787165</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4439130398</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4439142009</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Account Manager - Arabic Speaker (talabat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/account-manager-arabic-speaker-at-talabat-4439146844</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ERP Specialist (James L Williams Middle East)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-specialist-at-james-l-williams-middle-east-4439785377</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ERP Specialist (James L Williams Middle East)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-specialist-at-james-l-williams-middle-east-4439780664</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Other Posts (Optimal Healthcare Cayman)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/other-posts-at-optimal-healthcare-cayman-4439711687</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Charterhouse Middle East)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-charterhouse-middle-east-4439782645</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supply chain Admin and Expeditor (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-admin-and-expeditor-at-tasc-outsourcing-4439136650</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OPERATIONS MANAGER – WASTE MANAGEMENT (Imdaad Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-manager-%E2%80%93-waste-management-at-imdaad-group-4439799074</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Engineering, BI &amp; Governance Manager (Americana Restaurants)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-data-engineering-bi-governance-manager-at-americana-restaurants-4437209575</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Operations Manager (SupportRoom)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-manager-at-supportroom-4437253400</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRO Assistant (Dr. Sunny Medical Centre - UAE)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pro-assistant-at-dr-sunny-medical-centre-uae-4439784394</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Inspection Specialist (Confidential)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inspection-specialist-at-confidential-4435937822</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer (WOI.UAE)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-executive-officer-at-woi-uae-4437235802</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E-Commerce Operations Lead (Iqnoor Lifestyle) (Al Teneiji General Trading Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/e-commerce-operations-lead-iqnoor-lifestyle-at-al-teneiji-general-trading-co-l-l-c-4439778725</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Executive - Learning &amp; Development - Jumeirah Marsa Al Arab (Jumeirah)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-learning-development-jumeirah-marsa-al-arab-at-jumeirah-4437243809</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Region HR Specialist (Midea)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/region-hr-specialist-at-midea-4439130490</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Supply Chain Planner (Lobo Management)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-planner-at-lobo-management-4437207681</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Personal Assistant to Executive Office (Charismatic Dental Laboratory)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-to-executive-office-at-charismatic-dental-laboratory-4437209854</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Assistant Manager - Taxation (Apparel Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-taxation-at-apparel-group-4440000017</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Team Leader - Aircraft Interiors (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-aircraft-interiors-at-talentmate-4439772816</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Project Engineer - Fitout (Al Shirawi Interiors)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-fitout-at-al-shirawi-interiors-4440004279</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Accountant O2C /Accounts Receivable Executive (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/accountant-o2c-accounts-receivable-executive-at-tasc-outsourcing-4439139232</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -30,6 +30,7 @@
     <sheet name="11-07-2026" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="12-07-2026" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="13-07-2026" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="14-07-2026" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24146,6 +24147,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Stores Controller (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/stores-controller-at-air-arabia-4431724211</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Inventory / Equipment Manager (Dolphin Line Shipping LLC)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-equipment-manager-at-dolphin-line-shipping-llc-4440507541</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warehouse &amp; Logistics Supervisor (Changan MEA)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-logistics-supervisor-at-changan-mea-4439822542</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Team Leader (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-jd-com-4440031886</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>warehouse supervisor/ coordinator (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-supervisor-coordinator-at-tasc-outsourcing-4439820617</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NE Supervisor (Otis Elevator Co.)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ne-supervisor-at-otis-elevator-co-4439423046</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Information Technology Specialist (SPORTLUX)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-technology-specialist-at-sportlux-4439811959</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Factory Maintenance Engineer (LIPTON Teas and Infusions)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/factory-maintenance-engineer-at-lipton-teas-and-infusions-4440025879</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Technical Records Officer (flydubai)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-records-officer-at-flydubai-4440090021</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor (Amazon)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-at-amazon-4440093105</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Storekeeper (Unity Star Import and Export FZE LLC)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-at-unity-star-import-and-export-fze-llc-4439157534</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ecommerce Specialist (Eternell - Holistic Longevity)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ecommerce-specialist-at-eternell-holistic-longevity-4437612724</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Customer Service Associate - Cafe Kitchen | Retail | M&amp;S | UAE (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-associate-cafe-kitchen-retail-m-s-uae-at-al-futtaim-4440018357</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Administration with Car Rental Experience (VESLA MOTORS L.L.C)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-with-car-rental-experience-at-vesla-motors-l-l-c-4437651456</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Manager - IT Asset Management TECH - TOPS - End - User Services MIT (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-manager-it-asset-management-tech-tops-end-user-services-mit-at-talentmate-4440368864</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SAP Basis Consultant (Talal Group of Companies)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sap-basis-consultant-at-talal-group-of-companies-4437648823</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Construction Manager (CM) (SSK Group UAE)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-cm-at-ssk-group-uae-4437273081</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Executive Assistant – Travel and Tourism (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-%E2%80%93-travel-and-tourism-at-rtc1-recruitment-services-4437265589</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Presales Engineer – AV / ELV / ICT (Infolabs Global)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/presales-engineer-%E2%80%93-av-elv-ict-at-infolabs-global-4437601140</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Manager - Interface (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-interface-at-talentmate-4440376406</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Front Office Manager (Autograph Collection)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-manager-at-autograph-collection-4439803539</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Retail Sales Assistant (Women's clothing) (Lichi)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-sales-assistant-women-s-clothing-at-lichi-4437271769</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Warehouse Assistant (CSIS Project on Nuclear Issues (PONI))</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-at-csis-project-on-nuclear-issues-poni-4437636682</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Real Estate Admin (SRJ REAL ESTATE L.L.C)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/real-estate-admin-at-srj-real-estate-l-l-c-4437645908</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MCV Technical Superintendent (DP World)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mcv-technical-superintendent-at-dp-world-4440004863</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -31,6 +31,7 @@
     <sheet name="12-07-2026" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="13-07-2026" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="14-07-2026" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="15-07-2026" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25643,6 +25644,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sheet Metal Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sheet-metal-engineer-at-air-arabia-4431251927</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Document Controller (Parsons Corporation)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-parsons-corporation-4440542274</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Inventory Executive (PYTHAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Center Facility Manager (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-center-facility-manager-at-alibaba-cloud-4440941334</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant Manager – Purchases / Purchase Executive (Alhamad)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-%E2%80%93-purchases-purchase-executive-at-alhamad-4435648076</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Inventory / Equipment Manager (Dolphin Line Shipping LLC)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-equipment-manager-at-dolphin-line-shipping-llc-4440910315</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NE Supervisor (Otis Elevator Co.)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ne-supervisor-at-otis-elevator-co-4439423046</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor - UAE National, Amazon Logistics, RoW Reverse Logistics (Amazon)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-uae-national-amazon-logistics-row-reverse-logistics-at-amazon-4440810152</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Audits Specialist – Dosing &amp; Feeding Equipment- EMEA Region (Fuller)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/audits-specialist-%E2%80%93-dosing-feeding-equipment-emea-region-at-fuller-4440563392</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Supervisor (SSK Group UAE)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-at-ssk-group-uae-4438057635</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ecommerce Specialist (Sawaya Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ecommerce-specialist-at-sawaya-group-4440555884</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Center Director (The Tutoring Center Dubai)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/center-director-at-the-tutoring-center-dubai-4437668488</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Assistant Manager -Sales (Distribution) (Reed Recruitment Middle East)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-sales-distribution-at-reed-recruitment-middle-east-4440900884</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Clearance Documentation &amp; Sales Coordinator (Wilhelmsen Port Services)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/clearance-documentation-sales-coordinator-at-wilhelmsen-port-services-4440554141</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Construction Manager (Finishes) (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-finishes-at-cscec-middle-east-4437667658</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Warehouse &amp; Inventory Supervisor (Al Teneiji General Trading Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-inventory-supervisor-at-al-teneiji-general-trading-co-l-l-c-4440909569</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sales Coordinator (Resolute Dynamics)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-at-resolute-dynamics-4439843414</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Lead Estimator (Al Khoory Group مجموعة الخوري)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-estimator-at-al-khoory-group-%D9%85%D8%AC%D9%85%D9%88%D8%B9%D8%A9-%D8%A7%D9%84%D8%AE%D9%88%D8%B1%D9%8A-4437686161</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Platform Administrator (MultiBank Group)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/platform-administrator-at-multibank-group-4440566663</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Client Servicing Assistant Manager (Talent Higher)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/client-servicing-assistant-manager-at-talent-higher-4439862517</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flow Assurance Specialist - Mature Assets (Baker Hughes)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/flow-assurance-specialist-mature-assets-at-baker-hughes-4440829820</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Application Support Engineer, Trilogy (Remote) - $60,000/year USD (Crossover)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/application-support-engineer-trilogy-remote-%2460-000-year-usd-at-crossover-4439902887</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cloud Engineer (Global Role) (Career International 科锐国际)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cloud-engineer-global-role-at-career-international-%E7%A7%91%E9%94%90%E5%9B%BD%E9%99%85-4438053375</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist (SKM Air Conditioning LLC)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/talent-acquisition-specialist-at-skm-air-conditioning-llc-4438063405</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Executive – Sourcing (Purchasing) (We One)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-%E2%80%93-sourcing-purchasing-at-we-one-4437663513</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -32,6 +32,7 @@
     <sheet name="13-07-2026" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="14-07-2026" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="15-07-2026" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="16-07-2026" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27140,6 +27141,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Office Assistant - Facilities Mailing (Emirates)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-assistant-facilities-mailing-at-emirates-4438083494</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dubai – Professional Assistant (Hunton Andrews Kurth LLP)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dubai-%E2%80%93-professional-assistant-at-hunton-andrews-kurth-llp-4438450775</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4440637595</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administrative Assistant - Dubai (PJT Partners)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-dubai-at-pjt-partners-4423918553</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Front Office Assistant (Grosvenor House Dubai and Le Royal Meridien Beach Resort &amp; Spa)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-assistant-at-grosvenor-house-dubai-and-le-royal-meridien-beach-resort-spa-4438420051</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Secretary (DAMAC Properties)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/secretary-at-damac-properties-4438062871</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Executive Assistant to the Principal at Safa Community School (Safa Community School)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-the-principal-at-safa-community-school-at-safa-community-school-4440956530</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Office Administrator (Trelleborg Sealing Solutions)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-at-trelleborg-sealing-solutions-4440247489</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Admin Executive - Interior Fit-Out Firm - Dubai - Immediate Joiners (JobsInMass.com)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-interior-fit-out-firm-dubai-immediate-joiners-at-jobsinmass-com-4440946476</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Executive Assistant (SPORTLUX)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-sportlux-4440232305</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Facilities/Housekeeping Specialist (Stella Stays)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-housekeeping-specialist-at-stella-stays-4438489233</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Business Development Administrative Support (Sales and Operations) (Globe Williams International)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/business-development-administrative-support-sales-and-operations-at-globe-williams-international-4438476509</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cost Control And Planning Engineer (Emirates Industrial Panel (EIP))</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-control-and-planning-engineer-at-emirates-industrial-panel-eip-4441418325</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Purchase Officer - Façade Aluminum (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/purchase-officer-fa%C3%A7ade-aluminum-at-rtc1-recruitment-services-4438089813</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Hire Rightt - Executive Search &amp; HR Advisory)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-engineer-at-hire-rightt-executive-search-hr-advisory-4440231532</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cabin Services Assistant (Emirates)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cabin-services-assistant-at-emirates-4240426528</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senor Associate – Strategic Asset Allocation - Public Markets - SWF (Flynn and Chase)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senor-associate-%E2%80%93-strategic-asset-allocation-public-markets-swf-at-flynn-and-chase-4440512793</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chief Specialist - Service Providers (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-specialist-service-providers-at-roads-and-transport-authority-4438097218</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Warehouse Assistant (Vibrant Freight L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-assistant-at-vibrant-freight-l-l-c-4438451964</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Guest Service Assistant (Grosvenor House Dubai and Le Royal Meridien Beach Resort &amp; Spa)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/guest-service-assistant-at-grosvenor-house-dubai-and-le-royal-meridien-beach-resort-spa-4438400979</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Captain-A320 (UAE National) (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/captain-a320-uae-national-at-air-arabia-4398935330</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Site Engineer – Civil (Fresh Graduate) (Al Marwan Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-engineer-%E2%80%93-civil-fresh-graduate-at-al-marwan-group-4440213787</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Officer - Customer Experience (Commercial Bank International)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/officer-customer-experience-at-commercial-bank-international-4438076329</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Client Complaints Executive (Delta International Institute)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/client-complaints-executive-at-delta-international-institute-4438407418</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Technician Level 2 (AL Nabooda Automobiles LLC.)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technician-level-2-at-al-nabooda-automobiles-llc-4440945959</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -33,6 +33,7 @@
     <sheet name="14-07-2026" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="15-07-2026" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="16-07-2026" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="17-07-2026" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28637,6 +28638,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Office Administrator (JLT, Dubai) (eMagine Solutions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-jlt-dubai-at-emagine-solutions-4441655512</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Storekeeper (IIQAFGROUP)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-at-iiqafgroup-4439210087</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4441149967</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Office Manager (3 Month Contract) (Cooper Fitch)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-3-month-contract-at-cooper-fitch-4438700052</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Membership Administrator (Trump International Golf Club, Dubai)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/membership-administrator-at-trump-international-golf-club-dubai-4438711034</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4441172076</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warehouse Clerk (Liebherr Group)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-clerk-at-liebherr-group-4432633039</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Confidential)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-confidential-4441498144</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Branch Supervisor (Al Rostamani International Exchange)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/branch-supervisor-at-al-rostamani-international-exchange-4441931471</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Executive Assistant - 43835640334 (Somewhere)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-43835640334-at-somewhere-4441699429</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Engineering Admin Assistant (Marriott International)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-admin-assistant-at-marriott-international-4440799594</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Administrative Support Coordinator - Office of His Excellency Under Secretary (Experts Plus Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-support-coordinator-office-of-his-excellency-under-secretary-at-experts-plus-recruitment-services-4441942817</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Oracle SCM functional (Hire Rightt - Executive Search &amp; HR Advisory)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/oracle-scm-functional-at-hire-rightt-executive-search-hr-advisory-4441160637</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Technical Manager (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-technical-manager-at-cscec-middle-east-4438790281</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Operations Executive (Citizenship &amp; Co)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-at-citizenship-co-4438483938</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Executive Secretary (Rothana)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-secretary-at-rothana-4438760288</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Corporate Travel Coordinator - Business Travel (Confidential Careers)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/corporate-travel-coordinator-business-travel-at-confidential-careers-4441464372</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch / Hollister - Assistant Store Manager, Dubai (Abercrombie &amp; Fitch Co.)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/abercrombie-fitch-hollister-assistant-store-manager-dubai-at-abercrombie-fitch-co-4420135067</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Executive Assistant to CEO (Airwallex)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-ceo-at-airwallex-4429899420</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Resident Engineer (Bridges &amp; Infrastructure - Dubai) (Zutari)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/resident-engineer-bridges-infrastructure-dubai-at-zutari-4441454643</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SALES SUPPORT COORDINATOR (Napco National)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-support-coordinator-at-napco-national-4440930459</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Associate - Outbound Logistics Commercial (6 Months Contract only) (Emirates Global Aluminium (EGA))</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-associate-outbound-logistics-commercial-6-months-contract-only-at-emirates-global-aluminium-ega%E2%80%8B-4441456052</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ERP Systems Engineer (Odoo) (Group AMANA)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-systems-engineer-odoo-at-group-amana-4441142957</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate Manager - Corporate Services - Full-time (OVI)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-manager-corporate-services-full-time-at-ovi-4438732056</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Assistant Outlet Manager - Pierchic - Jumeirah Al Qasr (Jumeirah)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-outlet-manager-pierchic-jumeirah-al-qasr-at-jumeirah-4438792275</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -34,6 +34,7 @@
     <sheet name="15-07-2026" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="16-07-2026" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="17-07-2026" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="18-07-2026" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30134,6 +30135,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Office Coordinator (UniqPay)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-coordinator-at-uniqpay-4441389499</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Senior Executive Assistant (Citi)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-assistant-at-citi-4441303907</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive (Windmills Group)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-at-windmills-group-4439299247</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Parts Advisor - Dubai (Tesla)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/parts-advisor-dubai-at-tesla-4442104024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Residence Administrator (SO/ Uptown Dubai)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/residence-administrator-at-so-uptown-dubai-4439214737</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Retail Specialist (ACCEL HUMAN RESOURCE CONSULTANTS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-specialist-at-accel-human-resource-consultants-4439236362</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Warehouse Associate &amp; Delivery Associate (GMG)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-associate-delivery-associate-at-gmg-4441195580</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rooms Coordinator (Fairmont Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/rooms-coordinator-at-fairmont-hotels-resorts-4441189896</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Construction Manager (Tremco CPG Inc.)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-at-tremco-cpg-inc-4442176676</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Deputy Store Director (Louis Vuitton)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/deputy-store-director-at-louis-vuitton-4442127465</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Events Coordinator (Accor)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/events-coordinator-at-accor-4441394340</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Insurance Administrator (HR &amp; Payroll) (SAS International FZE)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/insurance-administrator-hr-payroll-at-sas-international-fze-4439285917</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Assistant Relationship Manager Analyst (Intesa Sanpaolo)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-relationship-manager-analyst-at-intesa-sanpaolo-4439244000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Store Director (Suitsupply)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-director-at-suitsupply-4330273412</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Payroll Manager (Kingston Stanley)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/payroll-manager-at-kingston-stanley-4441167990</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IT Engineer (Cambridge Educational Institute)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-engineer-at-cambridge-educational-institute-4439606154</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Salesforce Consultant (Dautom)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/salesforce-consultant-at-dautom-4441310173</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Team Leader (The Meydan Hotel)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-the-meydan-hotel-4439222571</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Developer Relations P2P 100% Remote (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/developer-relations-p2p-100%25-remote-at-talentmate-4442422112</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Personal Assistant (Asset Class Properties LLC)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-at-asset-class-properties-llc-4439230381</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Operation Specialist - Dubai (Emarati Only) (National Bank of Oman)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operation-specialist-dubai-emarati-only-at-national-bank-of-oman-4441195971</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Assistant Guest Relations Manager (Sunset Hospitality Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-guest-relations-manager-at-sunset-hospitality-group-4441170956</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Civil Infrastructure Engineer (MPH)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-infrastructure-engineer-at-mph-4439211944</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Career Consultant (Cambridge Educational Institute)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/career-consultant-at-cambridge-educational-institute-4439283941</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Expert Opportunity - Presentation Specialist ($80/hr, up to $1,600/week) (Ethos)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/expert-opportunity-presentation-specialist-%2480-hr-up-to-%241-600-week-at-ethos-4442128584</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -35,6 +35,7 @@
     <sheet name="16-07-2026" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="17-07-2026" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="18-07-2026" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="19-07-2026" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31631,6 +31632,1103 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workshop Planning Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-planning-engineer-at-air-arabia-4404092820</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reliability Maintenance Engineering Supervisor | UAE National (Amazon)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reliability-maintenance-engineering-supervisor-uae-national-at-amazon-4405817370</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QAQC CIVIL ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qaqc-civil-engineer-at-larsen-toubro-4414602231</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Butchery Supervisor - Distribution Center (talabat)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/butchery-supervisor-distribution-center-at-talabat-4391943600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant (leading joinery &amp; fit-out comany)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Engineering  Manager (talabat)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-at-talabat-4385227849</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Compliance Manager- Engineering, Quick Commerce (Amazon)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/compliance-manager-engineering-quick-commerce-at-amazon-4442482254</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Services Officer (Aldar Education)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-services-officer-at-aldar-education-3929440388</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Service &amp; Technical Lead (After Sales) | Building Products | Al Futtaim Contracting (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/service-technical-lead-after-sales-building-products-al-futtaim-contracting-at-al-futtaim-4433880646</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TESTING ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/testing-engineer-at-larsen-toubro-4442459567</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Information Technology Sales Manager (Alfalak Electronic Equipment &amp; Supplies Co.)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-information-technology-sales-manager-at-alfalak-electronic-equipment-supplies-co-4439675320</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Reporting and Presentation Specialist (Norconsult Telematics)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-reporting-and-presentation-specialist-at-norconsult-telematics-4420900086</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Field Engineer (Interdev Technology)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/field-engineer-at-interdev-technology-4441385827</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Principal Frontend Engineer (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/principal-frontend-engineer-at-talentmate-4442508012</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Admin Logistics (UAE National) (talabat)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-logistics-uae-national-at-talabat-4404266983</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist (Synolon Systems)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/talent-acquisition-specialist-at-synolon-systems-4439608664</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Analyst Assistant (Arabian Private Holdings)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-analyst-assistant-at-arabian-private-holdings-4441707945</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Supervisor / Foreman  (Interiors, Fit-out) (Crystal Fit Contracting)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-foreman-interiors-fit-out-at-crystal-fit-contracting-4439620272</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -36,6 +36,7 @@
     <sheet name="17-07-2026" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="18-07-2026" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="19-07-2026" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="20-07-2026" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34226,6 +34227,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Junior Operations Executive (Smileneo)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-operations-executive-at-smileneo-4439685574</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>House Manager (Confidential)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/house-manager-at-confidential-4442564880</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Office Coordinator - UAE National (Hilti Emirates)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-office-coordinator-uae-national-at-hilti-emirates-4440113409</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Procurement Specialist (MyVapery.ME)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-specialist-at-myvapery-me-4440104879</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Asset Manager (Dautom)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/software-asset-manager-at-dautom-4442008911</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Joinery Subcontractor Coordinator (Al Shirawi Interiors)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/joinery-subcontractor-coordinator-at-al-shirawi-interiors-4442582072</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Office Assistant (A&amp;I Group)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-assistant-at-a-i-group-4442023736</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Project Engineer - Interior Fit-Out - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-interior-fit-out-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4442009504</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Engr.- Equipment Maint. (Sundus)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engr-equipment-maint-at-sundus-4442580167</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Interior Fit-Out - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-interior-fit-out-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4442011485</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Junior Accountant (Florius Flowers)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-accountant-at-florius-flowers-4439694079</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Logistics Officer (MCG Asia)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-officer-at-mcg-asia-4442032019</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Associate Consultant (SEHATTI)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-consultant-at-sehatti-4440119355</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Dubai Municipality Approval - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-engineer-dubai-municipality-approval-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4442019191</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Logistics Assistant (Confidential Toys Company)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Sales - MSSP | Lumora | Dubai (Lumora Security)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pre-sales-mssp-lumora-dubai-at-lumora-security-4440109525</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Engr.  Cable Maintenance (Sundus)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sr-engr-cable-maintenance-at-sundus-4442566696</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data and Systems Analyst (EATX)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-and-systems-analyst-at-eatx-4440126297</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Applications Engineer (Quick Opening Closures) (NOV)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/applications-engineer-quick-opening-closures-at-nov-4412031046</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warehouse Supervisor (Je Dis Tout)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-supervisor-at-je-dis-tout-4442032170</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Procurement &amp; Supply Chain Specialist (KinzaHR)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-supply-chain-specialist-at-kinzahr-4442586098</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DotNet Developer with Advent (wealth management) (Virtusa)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dotnet-developer-with-advent-wealth-management-at-virtusa-4433723109</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Telesales Executive-Real Estate (Viviana Properties)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/telesales-executive-real-estate-at-viviana-properties-4440129056</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Technical Planning Officer (Long Term) (flydubai)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-technical-planning-officer-long-term-at-flydubai-4442563124</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Event Manager (Dubai, UAE) (SHEIN)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/event-manager-dubai-uae-at-shein-4442005661</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -37,6 +37,7 @@
     <sheet name="18-07-2026" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="19-07-2026" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="20-07-2026" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="21-07-2026" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35723,6 +35724,647 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Executive- Hard Services (Ejadah)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-hard-services-at-ejadah-4440128676</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Facility Specialist (Mammoet)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facility-specialist-at-mammoet-4443332175</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Reliability Maintenance Engineering Supervisor | UAE National (Amazon)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reliability-maintenance-engineering-supervisor-uae-national-at-amazon-4443036527</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Scaffolding Materials Specialist (CDHORIZON United Arab Emirates)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/scaffolding-materials-specialist-at-cdhorizon-united-arab-emirates-4432084735</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Executive- Soft Services (Ejadah)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-soft-services-at-ejadah-4440134428</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Warranty Administrator | Al-Futtaim Automotive | Electric Mobility (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warranty-administrator-al-futtaim-automotive-electric-mobility-at-al-futtaim-4442708061</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Logistics Executive, Deliverty Partner Manager (Amazon)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-executive-deliverty-partner-manager-at-amazon-4443036037</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Technical Superintendent (DP World)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-superintendent-at-dp-world-3840232372</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A183-ESG-Materials Control Specialist (Halliburton)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/a183-esg-materials-control-specialist-at-halliburton-4442052904</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Manager - Refinery (Caliberly® -  Recruitment Agency)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-refinery-at-caliberly%C2%AE-recruitment-agency-4443317111</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -38,6 +38,7 @@
     <sheet name="19-07-2026" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="20-07-2026" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="21-07-2026" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="22-07-2026" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36365,6 +36366,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Document Controller (Parsons Corporation)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-parsons-corporation-4443350793</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACES Specialist (Amazon)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/aces-specialist-at-amazon-4443538087</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Technical Superintendent - Dubai (Tomini Group)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-superintendent-dubai-at-tomini-group-4440451258</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Inventory Associate (Careem)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-associate-at-careem-4443758031</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Assistant Store Supervisor (talabat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-store-supervisor-at-talabat-4425805516</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Head of Planning (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-planning-at-tasc-outsourcing-4442612737</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4443733687</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Housekeeper (DAMAC Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-housekeeper-at-damac-hotels-resorts-4440460307</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Site Supervisor – Jewellery Retail Projects (Nakshathra Gold and Diamonds)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-supervisor-%E2%80%93-jewellery-retail-projects-at-nakshathra-gold-and-diamonds-4442923463</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Operations Executive (Zofeur)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-at-zofeur-4442991890</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chief of Staff (Pave Bank)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-of-staff-at-pave-bank-4443529551</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Supervisor, Apple Channel Stores, UAE (Apple)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-apple-channel-stores-uae-at-apple-4443753886</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cashier cum Admin (Autorun - OMODA JAECOO Dubai)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cashier-cum-admin-at-autorun-omoda-jaecoo-dubai-4440437802</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator (SARA Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-coordinator-at-sara-group-4440434937</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Personal Assistant to Chief Executive Officer (H&amp;S Real Estate Dubai)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-to-chief-executive-officer-at-h-s-real-estate-dubai-4443766553</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cashier (Accor)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cashier-at-accor-4442913963</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Assistant Boutique Manager (A. Lange &amp; Söhne)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-boutique-manager-at-a-lange-s%C3%B6hne-4442619638</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IT Systems Analyst (Orion Mining Inc)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-systems-analyst-at-orion-mining-inc-4442954349</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>secretary (Dubai Careers - A Smart Dubai Initiative)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/secretary-at-dubai-careers-a-smart-dubai-initiative-4443339942</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Store Manager (Apparel Group)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-at-apparel-group-4443338061</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Finance Coordinator - Accounts Payable (PxGeo)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/finance-coordinator-accounts-payable-at-pxgeo-4443525711</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Executive Secretary (Dubai Careers - A Smart Dubai Initiative)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-secretary-at-dubai-careers-a-smart-dubai-initiative-4443344744</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Customer Support Specialist (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-support-specialist-at-pulsemedianl-4443763521</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Civil Cost Control Engineer (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-cost-control-engineer-at-asia-prime-general-contracting-co-l-l-c-4443745267</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operations Manager (Events) (Talent Blueprint FZ LLC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-manager-events-at-talent-blueprint-fz-llc-4443732930</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -39,6 +39,7 @@
     <sheet name="20-07-2026" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="21-07-2026" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="22-07-2026" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="23-07-2026" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37862,6 +37863,1103 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Store Supervisor (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-supervisor-at-talentmate-4444254686</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Join the Elite Team at Ophiolite Hospitality, Hatta-Dubai In 2025 (Job Vacancy At Dubai)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/join-the-elite-team-at-ophiolite-hospitality-hatta-dubai-in-2025-at-job-vacancy-at-dubai-4444232748</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Office Manager (Xsolla)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-xsolla-4441089421</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Property and Leasing Admin (Home Plus Homes)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/property-and-leasing-admin-at-home-plus-homes-4444284335</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Store Supervisor (talabat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-supervisor-at-talabat-4425821451</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conrad Dubai Careers – Explore 5-Star Hotel Job Vacancies in Dubai (Job Vacancy At Dubai)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/conrad-dubai-careers-%E2%80%93-explore-5-star-hotel-job-vacancies-in-dubai-at-job-vacancy-at-dubai-4444247335</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Millennium Plaza Downtown Dubai Jobs Opening — Iconic Five-Star Hotel on Sheikh Zayed Road (Job Vacancy At Dubai)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/millennium-plaza-downtown-dubai-jobs-opening-%E2%80%94-iconic-five-star-hotel-on-sheikh-zayed-road-at-job-vacancy-at-dubai-4443797778</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch / Hollister - Assistant Store Manager, Dubai (myself.ae)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/abercrombie-fitch-hollister-assistant-store-manager-dubai-at-myself-ae-4443437486</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4443804025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Registration Coordinator - Billing &amp; Invoicing (GLOMACS Training &amp; Consultancy)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/registration-coordinator-billing-invoicing-at-glomacs-training-consultancy-4444262797</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Propulsion Manager (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/propulsion-manager-at-air-arabia-4435516948</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Document Controller (Khazna Data Centers)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-khazna-data-centers-4331080313</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Engineer - E&amp;S (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineer-e-s-at-larsen-toubro-4368638536</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Supply Chain Executive (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-executive-at-tasc-outsourcing-4443497231</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Document Controller (Emirates Electrical Engineering LLC)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-emirates-electrical-engineering-llc-4426781224</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Regional Asset Planner - Sub Sahara Africa (Baker Hughes)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-asset-planner-sub-sahara-africa-at-baker-hughes-4443991633</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4444279800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Salvaje Dubai Current Job Opportunities In Dubai UAE June 2025: 4 Hot Jobs Open (Job Vacancy At Dubai)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/salvaje-dubai-current-job-opportunities-in-dubai-uae-june-2025-4-hot-jobs-open-at-job-vacancy-at-dubai-4444240495</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -40,6 +40,7 @@
     <sheet name="21-07-2026" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="22-07-2026" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="23-07-2026" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="24-07-2026" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38960,6 +38961,1160 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Store Keeper (Sobha Constructions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-keeper-at-sobha-constructions-4434673238</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Team Assistant- IMEA Leadership Team (Brink’s Inc)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-assistant-imea-leadership-team-at-brink%E2%80%99s-inc-4437753969</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444090645</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Admin Executive (Real Estate) (Palazzo Versace Dubai)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-real-estate-at-palazzo-versace-dubai-4444423424</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist - Assistant Administrator (Remote) (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-entry-specialist-assistant-administrator-remote-at-pulsemedianl-4444769807</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444301212</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-cscec-middle-east-4441093875</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Administrative Officer (Ferrari Group)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-officer-at-ferrari-group-4441520424</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (RTB House)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-rtb-house-4431870272</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WANE GROUP Dubai Jobs – Explore New Vacancies (Job Vacancy At Dubai)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/wane-group-dubai-jobs-%E2%80%93-explore-new-vacancies-at-job-vacancy-at-dubai-4444773465</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Office Support Staff (VINSAK)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-support-staff-at-vinsak-4444051305</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shift Manager - Base Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shift-manager-base-maintenance-at-air-arabia-4436341858</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Center Facility Manager-Dubai (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-center-facility-manager-dubai-at-alibaba-cloud-4423621257</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Maintenance Engineer (Americana Restaurants)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-engineer-at-americana-restaurants-4444096369</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technical Office Manager (Experts Plus Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-office-manager-at-experts-plus-recruitment-services-4444440094</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Service Coordinator - Dubai (Rapiscan Systems)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/service-coordinator-dubai-at-rapiscan-systems-4432378899</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B1 - Certifying Engineer - Base Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/b1-certifying-engineer-base-maintenance-at-air-arabia-4426335805</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Assistant Manager- Central Operations (noon)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-central-operations-at-noon-4444423954</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Lindenberg Emirates LLC)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-lindenberg-emirates-llc-4441508250</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -41,6 +41,7 @@
     <sheet name="22-07-2026" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="23-07-2026" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="24-07-2026" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="25-07-2026" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40115,6 +40116,1503 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Junior Back Office Administrator (Joint Space Polyclinic LLC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-back-office-administrator-at-joint-space-polyclinic-llc-4444394686</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Document Controller - Site (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-site-at-talentmate-4445292241</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Engineering Storekeeper (Fairmont Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-storekeeper-at-fairmont-hotels-resorts-4444398260</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444651563</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Store officer (GEMS Education)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-officer-at-gems-education-4444334485</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Document Controller - Site (9E Global)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-site-at-9e-global-4444611277</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Front Office Assistant (Grosvenor House Dubai and Le Royal Meridien Beach Resort &amp; Spa)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-office-assistant-at-grosvenor-house-dubai-and-le-royal-meridien-beach-resort-spa-4438420051</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Title
+                    Patient Admin Coordinator (Mediclinic Middle East)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/title%0A-%0A-%0A-patient-admin-coordinator-at-mediclinic-middle-east-4444329749</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Abercrombie &amp; Fitch / Hollister - Assistant Store Manager, Dubai (myself.ae)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/abercrombie-fitch-hollister-assistant-store-manager-dubai-at-myself-ae-4444338691</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444642559</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Shamal Holding)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-shamal-holding-4444357184</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wheel &amp; Brake Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/wheel-brake-engineer-at-air-arabia-4445230636</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Spare Parts Specialist (Sungrow MENA &amp; Central Asia)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/spare-parts-specialist-at-sungrow-mena-central-asia-4444953429</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Sundus)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-sundus-4444330749</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Production Engineer (Gradiant)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/production-engineer-at-gradiant-4439783666</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor, Amazon Logistics (Amazon)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-amazon-logistics-at-amazon-4445263629</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Maintenance Coordinator (Americana Restaurants)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-coordinator-at-americana-restaurants-4441801284</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Technical Manager (Bahwan CyberTek)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-manager-at-bahwan-cybertek-4444333529</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UAE National Document Controller (Wood)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/uae-national-document-controller-at-wood-4444920999</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Receptionist (Al Safadi Hospitality)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receptionist-at-al-safadi-hospitality-4441586962</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Interior Fit-Out - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-interior-fit-out-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444660540</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ReConnect Membership Coordinator (Accor)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reconnect-membership-coordinator-at-accor-4444654175</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Design Studio Specialist-MUJ-UAE (myself.ae)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/design-studio-specialist-muj-uae-at-myself-ae-4444325929</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chief Specialist - OCC Governance (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-specialist-occ-governance-at-roads-and-transport-authority-4444307717</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IT Support (WYCON cosmetics)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-support-at-wycon-cosmetics-4444363638</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -42,6 +42,7 @@
     <sheet name="23-07-2026" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="24-07-2026" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="25-07-2026" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="26-07-2026" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41613,6 +41614,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Data Entry Specialist – Assistant Administrator (Remote) (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-entry-specialist-%E2%80%93-assistant-administrator-remote-at-pulsemedianl-4445367517</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444826429</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Personal Assistant to the CEO - Brand System Group (Infinite Fulfillment)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistant-to-the-ceo-brand-system-group-at-infinite-fulfillment-4442305163</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Remote Data Entry Specialist Admin (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/remote-data-entry-specialist-admin-at-pulsemedianl-4445370462</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Admin &amp; Office Coordinator (SARPi Group)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-office-coordinator-at-sarpi-group-4441894711</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Xpat Today)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-xpat-today-4442349413</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coordenador administrativo (Humaita Services FZCO)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Office Manager (Ultra Technology)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-ultra-technology-4442346490</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Airfreight Manager (Gulftainer)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/airfreight-manager-at-gulftainer-4442351451</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Membership Director (Aurora)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/membership-director-at-aurora-4445363302</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Civil Engineer - Dubai Municipality Approval - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/civil-engineer-dubai-municipality-approval-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444828124</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Logistics Executive | Retail | AlFuttaim Watches &amp; Jewellery (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-executive-retail-alfuttaim-watches-jewellery-at-al-futtaim-4436768240</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Accountant- Contracting (Bhatia general contracting)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-accountant-contracting-at-bhatia-general-contracting-4445321851</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Associate (Equiti Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-associate-at-equiti-group-4444829085</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Operations Manager (Invicta ANARA)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-manager-at-invicta-anara-4442318333</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Real Estate Listing (Coordinator) (Rose Island Real Estate)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/real-estate-listing-coordinator-at-rose-island-real-estate-4442302269</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Lead Solutions Architect &amp; Head of Engineering (Elevare Management Consultancy LLC)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-solutions-architect-head-of-engineering-at-elevare-management-consultancy-llc-4444683518</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sales Assistant - Dubai (Golden Goose)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-assistant-dubai-at-golden-goose-4427965174</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Inside Sales Consultant (Syscort Technologies)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inside-sales-consultant-at-syscort-technologies-4445355938</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Systems Engineer (Jordan) (Palo Alto Networks)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/systems-engineer-jordan-at-palo-alto-networks-4406789062</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Techno-Functional Project Manager - Saas Platform - Sharjah - Urgent Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/techno-functional-project-manager-saas-platform-sharjah-urgent-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444822105</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Principal System And Subsystem Engineer (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/principal-system-and-subsystem-engineer-at-talentmate-4445367560</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Techno-Functional Project Manager - Saas Platform - Sharjah - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/techno-functional-project-manager-saas-platform-sharjah-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4444835140</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Partner Solutions Engineer (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/partner-solutions-engineer-at-talentmate-4445359825</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Design Engineer - CAD &amp; SolidWorks - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/design-engineer-cad-solidworks-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444843106</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -43,6 +43,7 @@
     <sheet name="24-07-2026" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="25-07-2026" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="26-07-2026" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="27-07-2026" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43110,6 +43111,989 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>WAREHOUSE ADMINISTRATOR (DP World)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-administrator-at-dp-world-4445655883</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Join the Elite Team at Ophiolite Hospitality, Hatta-Dubai In 2025 (job-vacancy-at-dubai)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Office Administrator (PT. Guna Coalindo)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-administrator-at-pt-guna-coalindo-4442362895</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dubai Admin Lead (Bybit)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dubai-admin-lead-at-bybit-4444887198</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444868946</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Executive Assistant - VIP Support (Raqmiyat)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-vip-support-at-raqmiyat-4442813013</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Office Manager (Confidential)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-confidential-4445625669</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Construction Manager (Arabian Construction Co.)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-at-arabian-construction-co-4444881513</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4444861975</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4442826132</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Inventory Optimization Lead (Dyson)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-optimization-lead-at-dyson-4445909440</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Durability Specialist (TRACTEBEL)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/durability-specialist-at-tractebel-4442375113</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Service Specialist (O-MACHINES)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/service-specialist-at-o-machines-4445645458</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lead O&amp;M Engineer (TRACTEBEL)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-o-m-engineer-at-tractebel-4442362199</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TESTING ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/testing-engineer-at-larsen-toubro-4400516832</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Industrial Hygiene (Nestlé)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-industrial-hygiene-at-nestl%C3%A9-4445629880</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -44,6 +44,7 @@
     <sheet name="25-07-2026" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="26-07-2026" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="27-07-2026" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="28-07-2026" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44094,6 +44095,1503 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lead - Stores &amp; Inventory Control (Group AMANA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-stores-inventory-control-at-group-amana-4445429986</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Information Management Specialist (Hire Rightt - Executive Search &amp; HR Advisory)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-management-specialist-at-hire-rightt-executive-search-hr-advisory-4445119941</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Public Relations Specialist/ Manager (AMS International UAE)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-relations-specialist-manager-at-ams-international-uae-4445467339</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Operations Supervisor | UAE National only, FC Operations (Amazon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-supervisor-uae-national-only-fc-operations-at-amazon-4445926345</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Procurement Officer (Gulftainer)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-procurement-officer-at-gulftainer-4442846111</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>General Manager
+                                Urgent Hiring (Sana Pure Drinking Water)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-manager%0A%0A-urgent-hiring-at-sana-pure-drinking-water-4445950376</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor (Unilever)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-at-unilever-4445152295</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lead Site Reliability Engineer (ISA)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-site-reliability-engineer-at-isa-4445923673</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Document Controller - Design Office (Egis)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-design-office-at-egis-4445474675</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Principal Document Controller (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/principal-document-controller-at-mcdermott-international-ltd-4445958254</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Assistant Manager - R2R (edari)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-r2r-at-edari-4445944653</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sales Support Specialist (ePillars Systems)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-support-specialist-at-epillars-systems-4443206547</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Team Leader, Front Office, SIRO One Za'abeel (SIRO Hotels)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-front-office-siro-one-za-abeel-at-siro-hotels-4442837483</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Executive Secretary (Windmills Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-secretary-at-windmills-group-4443227024</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Admin cum Receptionist (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-cum-receptionist-at-rtc1-recruitment-services-4442840216</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Clinic Coordinator (Insights Psychology DMCC)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/clinic-coordinator-at-insights-psychology-dmcc-4443227752</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Investment Associate  - Family Office (Flynn and Chase)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-investment-associate-family-office-at-flynn-and-chase-4442744428</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Project Engineer | High Rise Building (ABU ALNAGA CONTRACTING)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-high-rise-building-at-abu-alnaga-contracting-4443247440</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Payroll Specialist (Kinetic Business Solutions)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/payroll-specialist-at-kinetic-business-solutions-4443210846</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Receptionist (UAEN) (Zutari)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receptionist-uaen-at-zutari-4445451532</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>General Manager (Light Steel/Aluminium) Fabrication Industry (Group of Factories Abduljalil Mahdi Mohd Alasmawi LLC)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/general-manager-light-steel-aluminium-fabrication-industry-at-group-of-factories-abduljalil-mahdi-mohd-alasmawi-llc-4443241772</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Project Engineer - Interior Fit-Out - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-interior-fit-out-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4445432927</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sales Executive (Patient Coordinator) (Intelligent Solutions HR)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-executive-patient-coordinator-at-intelligent-solutions-hr-4445484264</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estimation Engineer (Drydocks World)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/estimation-engineer-at-drydocks-world-4443244551</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Template-For Example (BYD EUROPE)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/template-for-example-at-byd-europe-4445134629</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -45,6 +45,7 @@
     <sheet name="26-07-2026" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="27-07-2026" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="28-07-2026" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="29-07-2026" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45592,6 +45593,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Storekeeper / Receiving Clerk (NH Collection Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-receiving-clerk-at-nh-collection-hotels-resorts-4433978619</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Storekeeper / Receiving Clerk (Minor Hotels)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-receiving-clerk-at-minor-hotels-4437405600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Coordinator IT Support - instashop (talabat)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/coordinator-it-support-instashop-at-talabat-4446047171</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Executive Assistant - Brooki (Arada)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-brooki-at-arada-4443622351</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4445728976</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4443670471</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Administrator Dnata Airport Operations (TALENTMATE)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrator-dnata-airport-operations-at-talentmate-4446519887</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Executive Personal Assistant (Vazir Group)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-personal-assistant-at-vazir-group-4443675670</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Operations, Accounts &amp; Admin Executive (KAYRA Bespoke)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-accounts-admin-executive-at-kayra-bespoke-4443694504</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4445742886</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Technical Procurement Officer (Sharjah, UAE) (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-procurement-officer-sharjah-uae-at-air-arabia-4446569476</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Guest Experience Representative - Level II (Shamal Holding)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/guest-experience-representative-level-ii-at-shamal-holding-4445744008</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Finance Administrator (Sean Cafe Taiwan)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/finance-administrator-at-sean-cafe-taiwan-4446521100</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>After-Sales &amp; Customer Support Executive – International Projects (Peergrowth)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/after-sales-customer-support-executive-%E2%80%93-international-projects-at-peergrowth-4446569350</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Estimation Engineer (Alight Steel Constructions Contracting L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/estimation-engineer-at-alight-steel-constructions-contracting-l-l-c-4446557492</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PA cum House Manager (The Talents Nation)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pa-cum-house-manager-at-the-talents-nation-4443674821</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopify E-commerce &amp; Inventory Supervisor (Aramtec Food Service)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shopify-e-commerce-inventory-supervisor-at-aramtec-food-service-4443682362</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Administrator (Emiratisation), dnata Airport Operations (dnata)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrator-emiratisation-dnata-airport-operations-at-dnata-4443617354</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Logistic Specialist (Taif Al Emarat | طيف الإمارات)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistic-specialist-at-taif-al-emarat-%D8%B7%D9%8A%D9%81-%D8%A7%D9%84%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA-4443270831</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Lead Planning Engineer-STP (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-planning-engineer-stp-at-air-arabia-4446195831</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Reliability Maintenance Engineering Planner, RME (Amazon)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/reliability-maintenance-engineering-planner-rme-at-amazon-4446358082</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Camp Boss (SAM Building Contracting LLC)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/camp-boss-at-sam-building-contracting-llc-4443283865</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Inventory &amp; Loss Prevention Specialist (Avolta)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-loss-prevention-specialist-at-avolta-4443268705</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Production Planning Officer (Emirates)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/production-planning-officer-at-emirates-4443670590</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AOV MOV Supervisor (MPH)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/aov-mov-supervisor-at-mph-4444103088</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -46,6 +46,7 @@
     <sheet name="27-07-2026" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="28-07-2026" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="29-07-2026" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="30-07-2026" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48585,6 +48586,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Performance Live Center Planner (SLB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/performance-live-center-planner-at-slb-4444188430</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Retail Operations &amp; Logistics Executive (Sportswear) (NADIA)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/retail-operations-logistics-executive-sportswear-at-nadia-4444530366</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Engineering Training Manager (Air Arabia Academy)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-training-manager-at-air-arabia-academy-4446400491</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Assistant Technical Superintendent (SYNCRO SHIPPING)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AOV MOV Supervisor (MPH)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/aov-mov-supervisor-at-mph-4444103088</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Workshop Coordinator (ALBA CORP)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-coordinator-at-alba-corp-4444146892</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HR Specialist – HRIS &amp; Payroll (Sharjah National Oil Corporation (SNOC))</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-specialist-%E2%80%93-hris-payroll-at-sharjah-national-oil-corporation-snoc-4446703635</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Operations Executive (dubizzle)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-at-dubizzle-4444152312</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Production Supervisor (Emerson)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/production-supervisor-at-emerson-4446820455</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4444502941</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cashier (The Food and Beverage Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cashier-at-the-food-and-beverage-group-4444149892</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Executive Secretary (Windmills Group)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-secretary-at-windmills-group-4444553101</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Manager – ECommerce (D2C) (Lobo Management)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-manager-%E2%80%93-ecommerce-d2c-at-lobo-management-4444116562</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Lead Infrastructure &amp; Cloud Engineer (Olik Global)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-infrastructure-cloud-engineer-at-olik-global-4444521673</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warehouse Helper (Nabors Industries)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-helper-at-nabors-industries-4444520374</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lead Infrastructure &amp; Cloud Engineer (Olik Global)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/lead-infrastructure-cloud-engineer-at-olik-global-4444527542</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dispatch &amp; Delivery Executive (PrepHero)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dispatch-delivery-executive-at-prephero-4443697081</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Assistant Storekeeper (Egis)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-storekeeper-at-egis-4445976217</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Relationship Manager (12 vacancies) (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relationship-manager-12-vacancies-at-rtc1-recruitment-services-4444525500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Car Sales &amp; Consignment Specialist (Approved Automotive)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/car-sales-consignment-specialist-at-approved-automotive-4444529828</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Information Technology Manager (So!)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-technology-manager-at-so%21-4446827283</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tendering Engineer (Center Core)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/tendering-engineer-at-center-core-4444528769</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Junior Planning Engineer (K4 Group)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-planning-engineer-at-k4-group-4446572653</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ICT Infrastructure - Enterprise Solutions Architect (e&amp;)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ict-infrastructure-enterprise-solutions-architect-at-e-4444139038</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Boutique Manager - Luxury Watches Boutique (Seddiqi Holding)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/boutique-manager-luxury-watches-boutique-at-seddiqi-holding-4446702575</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -47,6 +47,7 @@
     <sheet name="28-07-2026" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="29-07-2026" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="30-07-2026" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="31-07-2026" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50082,6 +50083,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4446960942</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Data Entry Coordinator (Remote) (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-entry-coordinator-remote-at-pulsemedianl-4447249233</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Store In-Charge (GMG)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-in-charge-at-gmg-4445072254</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4446978119</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator (Vacation Homes by Provident)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-coordinator-at-vacation-homes-by-provident-4447263089</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Emirates Global Aluminium (EGA))</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-emirates-global-aluminium-ega%E2%80%8B-4447267287</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Executive Assistant to General Manager - Marriott Executive Apartments Sheikh Zayed Road (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-general-manager-marriott-executive-apartments-sheikh-zayed-road-at-marriott-executive-apartments-4446941032</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Personal Assistance (Julius Baer)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/personal-assistance-at-julius-baer-4446743880</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Admin Assistant (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-assistant-at-marriott-executive-apartments-4446935098</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Time Keeper (Futurelink HR Consultancy)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/time-keeper-at-futurelink-hr-consultancy-4447272279</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Technical Coordinator (Fit out) (Al Shirawi Interiors)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-coordinator-fit-out-at-al-shirawi-interiors-4446738644</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MEP Coordinator (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mep-coordinator-at-asia-prime-general-contracting-co-l-l-c-4445072055</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Operation Coordinator (NAFFCO Careers)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operation-coordinator-at-naffco-careers-4446775017</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Relocate to Dubai | Luxury Hospitality Careers | General Manager |  Dubai, UAE (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relocate-to-dubai-luxury-hospitality-careers-general-manager-dubai-uae-at-ali-professional-4447026192</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HPC and Storage Technology Consultant (Hewlett Packard Enterprise)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hpc-and-storage-technology-consultant-at-hewlett-packard-enterprise-4447055132</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pool Technician (Royal Caribbean International)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pool-technician-at-royal-caribbean-international-4446761270</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Cost Control Engineer (Global Process Systems)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-control-engineer-at-global-process-systems-4447281883</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Asset Management Specialist | Emirati Talent (Majid Al Futtaim)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/asset-management-specialist-emirati-talent-at-majid-al-futtaim-4445072979</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Smart City Technical Lead (Honeywell Technologies)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/smart-city-technical-lead-at-honeywell-technologies-4446760323</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ITS Engineer (Parsons Corporation)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/its-engineer-at-parsons-corporation-4446061313</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Operations Coordinator (AMPSY CONSULTANCY LLC)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-coordinator-at-ampsy-consultancy-llc-4445029604</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kubernetes Administrator (MAGNOOS Information Systems)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/kubernetes-administrator-at-magnoos-information-systems-4387514676</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Assistant Manager Learning Platforms (Transguard Workforce Solutions)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-learning-platforms-at-transguard-workforce-solutions-4446990468</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Relocate to Dubai | Luxury Hospitality Careers | Head Sommelier | Fine Dining | Dubai (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/relocate-to-dubai-luxury-hospitality-careers-head-sommelier-fine-dining-dubai-at-ali-professional-4447048324</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DUCT FOREMAN (BAT Technical Services LLC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/duct-foreman-at-bat-technical-services-llc-4445088064</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -48,6 +48,7 @@
     <sheet name="29-07-2026" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="30-07-2026" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="31-07-2026" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="01-08-2026" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51579,6 +51580,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Spare Parts Officer (KONE)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/spare-parts-officer-at-kone-4430953683</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Operations Executive, (UAE National), Amazon Now, UFG (Amazon)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-uae-national-amazon-now-ufg-at-amazon-4447574136</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Assistant Manager -Logistics (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-logistics-at-larsen-toubro-4439057807</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Warranty Executive | Al-Futtaim Motors | Toyota (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warranty-executive-al-futtaim-motors-toyota-at-al-futtaim-4447291664</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dispatcher (Confidential)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/dispatcher-at-confidential-4447541439</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Team Leader (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-jd-com-4447295512</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fleet Supervisor (Logistics). (Al Khayyat Investments (AKI))</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/fleet-supervisor-logistics-at-al-khayyat-investments-aki-4445508535</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>QA/QC Manager-CCGT (Aljomaih Energy and Water Company)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qa-qc-manager-ccgt-at-aljomaih-energy-and-water-company-4447506606</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Store Manager (MINIMALIST)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-at-minimalist-4445503948</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Document Control Lead (Rebel Recruiters)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-control-lead-at-rebel-recruiters-4445096383</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IT Support Engineer L1 (VaporVM)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-support-engineer-l1-at-vaporvm-4447130805</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Site Engineer / Supervisor (K4 Group)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-engineer-supervisor-at-k4-group-4447524324</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Buildings Maintenance Coordinator (Vakson Development)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/buildings-maintenance-coordinator-at-vakson-development-4445571902</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sales Manager (Office Furniture) (NADIA)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-manager-office-furniture-at-nadia-4445502530</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Junior Purchase Officer (Caliberly® -  Recruitment Agency)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-purchase-officer-at-caliberly%C2%AE-recruitment-agency-4447509946</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Driver - Front Office (Al Bandar Rotana &amp; Al Bandar Arjaan by Rotana)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/driver-front-office-at-al-bandar-rotana-al-bandar-arjaan-by-rotana-4435905080</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Fresh Graduates) (Hamdan Bin Mohammed Smart University)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-engineer-fresh-graduates-at-hamdan-bin-mohammed-smart-university-4445590044</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CRM executive (Zofeur)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/crm-executive-at-zofeur-4445506530</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Customer Care Center - Executive (myself.ae)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-care-center-executive-at-myself-ae-4447408026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cost Control Engineer (D&amp;A Consult)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-control-engineer-at-d-a-consult-4445505107</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Associate Certification Tech (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-certification-tech-at-mcdermott-international-ltd-4401774387</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Bid Manager (Siemens Energy)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-bid-manager-at-siemens-energy-4446984935</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Community Manager (Arabic speaker) (Palazzo Versace Dubai)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/community-manager-arabic-speaker-at-palazzo-versace-dubai-4447511318</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Testing, Inspection &amp; Certification (TIC) Technician (Motive Offshore Group Ltd)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/testing-inspection-certification-tic-technician-at-motive-offshore-group-ltd-4446996552</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Customer Relationship Management Administrator (La Foret Real Estate L.L.C)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-relationship-management-administrator-at-la-foret-real-estate-l-l-c-4445504724</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -49,6 +49,7 @@
     <sheet name="30-07-2026" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="31-07-2026" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="01-08-2026" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="02-08-2026" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53076,6 +53077,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>warehouse incharge (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-incharge-at-burjline-builders-4447486530</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sales Admin (Semasocial)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-admin-at-semasocial-4447853162</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4447631644</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4447632582</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-burjline-builders-4447474806</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Accounts Payable / General Cashier / Paymaster - Marriott Executive Apartments Sheikh Zayed Road (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/accounts-payable-general-cashier-paymaster-marriott-executive-apartments-sheikh-zayed-road-at-marriott-executive-apartments-4447479919</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Admin cum Executive Assistant (AS CORP)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-cum-executive-assistant-at-as-corp-4445512627</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Payroll and Reporting Officer (Zayed University)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-payroll-and-reporting-officer-at-zayed-university-4402264807</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Offic Assistant (Stellar House EG)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/offic-assistant-at-stellar-house-eg-4447881323</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Temporary IT Helpdesk Support Specialist (TAJMAC Global FZE)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/temporary-it-helpdesk-support-specialist-at-tajmac-global-fze-4447870597</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IT Solution Architect (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-solution-architect-at-burjline-builders-4447490477</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Interior Fit-Out - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-interior-fit-out-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4447629707</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Project Coordinator - Interior Fit-Out - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-coordinator-interior-fit-out-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4447641444</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Application Support Specialist – Banking Applications (UAE) (emagine)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-application-support-specialist-%E2%80%93-banking-applications-uae-at-emagine-4440751379</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Project Engineer - Interior Fit-Out - Dubai - Immediate Joiners (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-interior-fit-out-dubai-immediate-joiners-at-sanvi-engineering-and-business-consulting-solutions-4447636539</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Front Desk Supervisor - Marriott Executive Apartments Sheikh Zayed Road (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/front-desk-supervisor-marriott-executive-apartments-sheikh-zayed-road-at-marriott-executive-apartments-4447487750</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Construction Tech (Fab) (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-tech-fab-at-mcdermott-international-ltd-4439541461</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Regional Asset Planner - Sub Sahara Africa (Baker Hughes)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-asset-planner-sub-sahara-africa-at-baker-hughes-4443991633</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Supervisor-Front Office (Marriott Executive Apartments)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-front-office-at-marriott-executive-apartments-4447492580</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>We are hiring : SOFTWARE SUPPORT &amp; TESTER (Burjline Builders)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/we-are-hiring-software-support-tester-at-burjline-builders-4447486532</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Procurement Assistant / Purchasing Assistant / Procurement Coordinator (Untuk Lulusan Baru &amp; Early Career NEXT)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-assistant-purchasing-assistant-procurement-coordinator-at-untuk-lulusan-baru-early-career-next-4445839310</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Project Manager - High-Rise Construction (Talents Tide)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-manager-high-rise-construction-at-talents-tide-4447496269</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sales Manager - Staffing/Manpower (Confidential)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-manager-staffing-manpower-at-confidential-4447786352</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1 day ago</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Help Desk Analyst (Sophrosyne UAE)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/help-desk-analyst-at-sophrosyne-uae-4445837266</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Assistant Brand Manager (Agthia Group PJSC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-brand-manager-at-agthia-group-pjsc-4445590601</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -50,6 +50,7 @@
     <sheet name="31-07-2026" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="01-08-2026" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="02-08-2026" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="03-08-2026" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54573,6 +54574,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Storekeeper - Spare Parts (Automotive) (Abdulla Al Masaood and Sons Group (AMS Group))</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-spare-parts-automotive-at-abdulla-al-masaood-and-sons-group-ams-group-4448122135</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>مساعد اداري (General Pension and Social Security Authority (GPSSA))</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%D9%85%D8%B3%D8%A7%D8%B9%D8%AF-%D8%A7%D8%AF%D8%A7%D8%B1%D9%8A-at-general-pension-and-social-security-authority-gpssa-4448135534</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Admin Executive - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/admin-executive-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4447677807</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Administrative Executive - Food &amp; Beverage (Arada)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-executive-food-beverage-at-arada-4445883383</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Remote Virtual Administrative Assistant (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/remote-virtual-administrative-assistant-at-pulsemedianl-4448129232</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Administration Executive - Corporate Services - Dubai - Immediate Hiring (Sanvi Engineering And Business Consulting Solutions)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administration-executive-corporate-services-dubai-immediate-hiring-at-sanvi-engineering-and-business-consulting-solutions-4447695401</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Remote Virtual Administrative Assistant (PulseMediaNL)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/remote-virtual-administrative-assistant-at-pulsemedianl-4448129233</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ERP Support Engineer/Analyst (ASIA Prime General Contracting Co. L.L.C.)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/erp-support-engineer-analyst-at-asia-prime-general-contracting-co-l-l-c-4445888207</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Office Coordinator (Michael Page)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-coordinator-at-michael-page-4448141830</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Executive Assistant to C Suite (Americana Restaurants)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-to-c-suite-at-americana-restaurants-4445861864</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trưởng Phòng Nhân Sự &amp; Chuyên viên Phát triển Đối tác (KUP Co. Ltd.,)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/tr%C6%B0%E1%BB%9Fng-ph%C3%B2ng-nh%C3%A2n-s%E1%BB%B1-chuy%C3%AAn-vi%C3%AAn-ph%C3%A1t-tri%E1%BB%83n-%C4%91%E1%BB%91i-t%C3%A1c-at-kup-co-ltd-4447687520</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technical Manager (Polymer) (NADIA)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-manager-polymer-at-nadia-4445866558</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Technical Manager (Civil Construction) (Sobha Siniya Island)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-manager-civil-construction-at-sobha-siniya-island-4447640877</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Document Controller (POLARIS-NGF program)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-polaris-ngf-program-4445899230</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Project Planning Engineer (AAm Est.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-planning-engineer-at-aam-est-4445883502</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Supply Chain Executive - Arabic speaker (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-executive-arabic-speaker-at-tasc-outsourcing-4447688693</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Technical Support Engineer (Women First Jobs)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-engineer-at-women-first-jobs-4445868439</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Customer Service Supervisor (Consumer) (Al Khayyat Investments (AKI))</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-supervisor-consumer-at-al-khayyat-investments-aki-4445871534</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Planning Engineer (TMC Group)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-tmc-group-4445874464</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Security Operations Center Engineer (Tandem Interim)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/security-operations-center-engineer-at-tandem-interim-4445870689</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Public Relations Officer (Metaworld Consultant)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/public-relations-officer-at-metaworld-consultant-4445854366</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Protection Officer (Sungrow MENA &amp; Central Asia)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-protection-officer-at-sungrow-mena-central-asia-4448165441</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Workforce Transformation Specialist (Adecco)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workforce-transformation-specialist-at-adecco-4440541370</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Engineering Technician (Excel Career Solutions)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-technician-at-excel-career-solutions-4445863822</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEO Specialist (Remote) (Hub Drives Line Rental Car LLC SOC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/seo-specialist-remote-at-hub-drives-line-rental-car-llc-soc-4445888099</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -51,6 +51,7 @@
     <sheet name="01-08-2026" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="02-08-2026" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="03-08-2026" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="04-08-2026" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56070,6 +56071,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Managment excutive (VITALMED)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/managment-excutive-at-vitalmed-4448802974</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Technical Support Supervisor (SLB)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-support-supervisor-at-slb-4445891515</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Maintenance Planning Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-planning-engineer-at-air-arabia-4448835276</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Facilities Lead - TET (SLB)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-lead-tet-at-slb-4446253950</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Production Planning Engineer - PPC (Emirates)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/production-planning-engineer-ppc-at-emirates-4446224890</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Maintenance Supervisor (Al Salah Holding)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-supervisor-at-al-salah-holding-4445897644</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Operations Executive (Abu Dhabi) (dubizzle)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-abu-dhabi-at-dubizzle-4446217007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>اعلان وظائف (SINA Investment Group)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%D8%A7%D8%B9%D9%84%D8%A7%D9%86-%D9%88%D8%B8%D8%A7%D8%A6%D9%81-at-sina-investment-group-4442369335</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr Technical Superintendent (LPG) (Bahri | البحري)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sr-technical-superintendent-lpg-at-bahri-%D8%A7%D9%84%D8%A8%D8%AD%D8%B1%D9%8A-4446606720</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Operations Executive (Gateworth Group)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-at-gateworth-group-4446200220</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Indigo Living)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-indigo-living-4446203931</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Protection Engineer | Corporate Services | Group Tech &amp; Dig Platforms (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-protection-engineer-corporate-services-group-tech-dig-platforms-at-al-futtaim-4448327171</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Receiving Clerk (Hyatt Place)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/receiving-clerk-at-hyatt-place-4448316023</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Construction Manager (Albatha Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/construction-manager-at-albatha-group-4448171309</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Head of Engineering - Customer Experience (noon)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-engineering-customer-experience-at-noon-4448828105</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Case Owner and Product Support Manager (Rolls-Royce)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/case-owner-and-product-support-manager-at-rolls-royce-4448156554</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FM Supervisor Jobs in Dubai, UAE | Facilities Management Supervisor (Ejobsboard)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sheet Metal Certifying Technician (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sheet-metal-certifying-technician-at-air-arabia-4440041498</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Government Affairs and Public Policy Manager (Google)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/government-affairs-and-public-policy-manager-at-google-4448250418</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Indigo Living UAE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-indigo-living-uae-4446212164</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Examination Officer - AY2627 (GEMS Education)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/examination-officer-ay2627-at-gems-education-4448255107</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior HSE Officer (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-hse-officer-at-cscec-middle-east-4446291439</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Operations Administrator / Scheduler (PPK Contracting)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-administrator-scheduler-at-ppk-contracting-4446600553</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Information Technology Executive (Windmills Group)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-technology-executive-at-windmills-group-4446606138</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Contract Administrator (ASGC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/contract-administrator-at-asgc-4446605993</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -52,6 +52,7 @@
     <sheet name="02-08-2026" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="03-08-2026" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="04-08-2026" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="05-08-2026" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57567,6 +57568,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MFP &amp; Print Solutions Team (Multiple Openings) (Epic Solutions)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mfp-print-solutions-team-multiple-openings-at-epic-solutions-4448959953</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shift Manager - Line Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/shift-manager-line-maintenance-at-air-arabia-4448889241</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Engineering Manager (talabat)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-at-talabat-4447377584</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Inventory Control and Quality Assurance Supervisor - UAE National (Amazon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/inventory-control-and-quality-assurance-supervisor-uae-national-at-amazon-4448868252</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Engineering Manager / Logistics Manager (Delta Housing - Constructions)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-logistics-manager-at-delta-housing-constructions-4446621542</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Logistics Specialist (Dr Scent)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-specialist-at-dr-scent-4448520065</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Planning Engineer (Lindenberg Emirates LLC)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-engineer-at-lindenberg-emirates-llc-4446698174</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FM Coordinator (YAEMCO LLC)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/fm-coordinator-at-yaemco-llc-4449439467</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Office Manager (Maandag®)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-maandag%C2%AE-4448279480</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Superintendent - Env. JA/AT (Emirates Global Aluminium (EGA))</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-superintendent-env-ja-at-at-emirates-global-aluminium-ega%E2%80%8B-4448859177</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Operations &amp; Administrative Executive (THE·TEAM)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-administrative-executive-at-the%C2%B7team-4448850520</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Director of Engineering (Al Zorah Beach Resort)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/director-of-engineering-at-al-zorah-beach-resort-4448521318</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chief of Staff (The Ivy)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-of-staff-at-the-ivy-4448957506</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Head of Infrastructure (Zand)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-infrastructure-at-zand-4446637381</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Office Manager (1 year contract) (MCG Talent)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-1-year-contract-at-mcg-talent-4446613595</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>🇦🇪 Site Engineer | Mega Construction Projects | Dubai, UAE | Turn Engineering into Reality. Build Where the World Looks (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%F0%9F%87%A6%F0%9F%87%AA-site-engineer-mega-construction-projects-dubai-uae-turn-engineering-into-reality-build-where-the-world-looks-at-ali-professional-4449467143</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator &amp; Office Manager-12 Month Contract (Neuberger)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-coordinator-office-manager-12-month-contract-at-neuberger-4448568149</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Warehouse operation Specialist (Emerson)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-operation-specialist-at-emerson-4448849715</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Operations Support Administrative (JCDecaux Middle East)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-support-administrative-at-jcdecaux-middle-east-4448856041</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Store Supervisor (GMG)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-supervisor-at-gmg-4446641405</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Technical Manager – Cloud Infrastructure Engineering (Emirates)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-manager-%E2%80%93-cloud-infrastructure-engineering-at-emirates-4446671512</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Site Inspector - Materials (Dubai Infrastructure Projects) (Khatib &amp; Alami)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/site-inspector-materials-dubai-infrastructure-projects-at-khatib-alami-4449008051</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BSS L2 SME (Ericsson)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/bss-l2-sme-at-ericsson-4448280551</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Maintenance Manager (FL Technics)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-manager-at-fl-technics-4434856177</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Document Controller-Project Execution (DAMAC Properties)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-project-execution-at-damac-properties-4448876894</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -53,6 +53,7 @@
     <sheet name="03-08-2026" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="04-08-2026" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="05-08-2026" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="06-08-2026" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -59064,6 +59065,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Customer Support Specialist (NeoMiners)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-support-specialist-at-neominers-4449468845</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sheet Metal Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sheet-metal-engineer-at-air-arabia-4431251927</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Service Delivery Engineer (Motive Offshore Group Ltd)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/service-delivery-engineer-at-motive-offshore-group-ltd-4448980418</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Audits Specialist – Dosing &amp; Feeding Equipment- EMEA Region (Fuller)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/audits-specialist-%E2%80%93-dosing-feeding-equipment-emea-region-at-fuller-4440563392</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Material Planner (ABB)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/material-planner-at-abb-4449652816</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Logistic Specialist - PERFUME INDUSTRY (Taif Al Emarat | طيف الإمارات)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistic-specialist-perfume-industry-at-taif-al-emarat-%D8%B7%D9%8A%D9%81-%D8%A7%D9%84%D8%A5%D9%85%D8%A7%D8%B1%D8%A7%D8%AA-4448020544</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Building Manager (TASC Outsourcing)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/building-manager-at-tasc-outsourcing-4448995490</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Document Controller - Design Office (Egis)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-design-office-at-egis-4445474675</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Completions Specialist (Fab) (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/completions-specialist-fab-at-mcdermott-international-ltd-4449636749</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Manager - EV &amp; Operations (noon)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-ev-operations-at-noon-4450202011</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI/ML ops (TalentFinderX)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/ai-ml-ops-at-talentfinderx-4449600061</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Planning Manager (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/planning-manager-at-cscec-middle-east-4447398452</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>خبير الذكاء الاصطناعي - Artificial Intelligence Expert (Ministry of Economy &amp; Tourism)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%D8%AE%D8%A8%D9%8A%D8%B1-%D8%A7%D9%84%D8%B0%D9%83%D8%A7%D8%A1-%D8%A7%D9%84%D8%A7%D8%B5%D8%B7%D9%86%D8%A7%D8%B9%D9%8A-artificial-intelligence-expert-at-ministry-of-economy-tourism-4449376263</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MDM Lead (Virtusa)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mdm-lead-at-virtusa-4444103112</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Office Manager &amp; Sales Coordinator (Luxbuild Technical Services)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Purchasing Engineer | alfanar Electric (alfanar)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/purchasing-engineer-alfanar-electric-at-alfanar-4449106715</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Production Engineer (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/production-engineer-at-mcdermott-international-ltd-4449626813</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Administrative Officer (Depa Group)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-administrative-officer-at-depa-group-4448082964</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Vice President of Engineering (HR Ways - Hiring Tech Talent)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/vice-president-of-engineering-at-hr-ways-hiring-tech-talent-4449361578</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marine | Shipbuilding | Oil &amp; Gas - Professionals &amp; Skilled Trades (EzerHR)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/marine-shipbuilding-oil-gas-professionals-skilled-trades-at-ezerhr-4448069126</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Maintenance Planning Engineer - Jakarta Recruitment Event (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-planning-engineer-jakarta-recruitment-event-at-air-arabia-4449695505</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Deputy Store Director (Louis Vuitton)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/deputy-store-director-at-louis-vuitton-4440847995</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NOC Coordinator (eMinds)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/noc-coordinator-at-eminds-4448404026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sales Coordinator | Al-Futtaim Automotive | Electric Mobility (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-coordinator-al-futtaim-automotive-electric-mobility-at-al-futtaim-4449474500</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Nursery Manager (Nathan &amp; Nathan)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/nursery-manager-at-nathan-nathan-4450210533</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -54,6 +54,7 @@
     <sheet name="04-08-2026" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="05-08-2026" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="06-08-2026" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="07-08-2026" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60561,6 +60562,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR &amp; Administration Executive (Dubai Jobs in Paper)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hr-administration-executive-at-dubai-jobs-in-paper-4450662040</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chief Engineer (Minor Hotels)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-engineer-at-minor-hotels-4450288045</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chief Engineer (Anantara Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-engineer-at-anantara-hotels-resorts-4450265060</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Logistics Engineer (CSCEC Middle East)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-logistics-engineer-at-cscec-middle-east-4448411786</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Critical Environment Program Manager (Microsoft)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/critical-environment-program-manager-at-microsoft-4450253291</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Team Leader (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-jd-com-4450236329</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pricing Executive (Dubai Jobs in Paper)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pricing-executive-at-dubai-jobs-in-paper-4450645922</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IT Engineering Manager — Endpoint, SaaS (talabat)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-engineering-manager-%E2%80%94-endpoint-saas-at-talabat-4449755199</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>O&amp;M Engineer (Mid-Level) (Etihad Energy Services Company (Etihad ESCO))</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/o-m-engineer-mid-level-at-etihad-energy-services-company-etihad-esco-4450024496</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Office Manager &amp; Front of House (Xpin AI)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-front-of-house-at-xpin-ai-4448431820</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Engineering Efficiency &amp; Assurance Lead (Hays)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-efficiency-assurance-lead-at-hays-4448421029</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Project Controls Admin (UAE National) (Wood)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-controls-admin-uae-national-at-wood-4450069029</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Operations Supervisor - Express (Zajel_official)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-supervisor-express-at-zajel-official-4450065061</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Marine Repair Manager (Greens)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/marine-repair-manager-at-greens-4449743694</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Project Manager (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-manager-at-larsen-toubro-4432584319</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer (Zofeur)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-technology-officer-at-zofeur-4450247692</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Process Engineer (Faham Group)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/process-engineer-at-faham-group-4448748039</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Flight Operations Engineer (flydubai)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/flight-operations-engineer-at-flydubai-4450288918</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HPC and Storage Technology Consultant (Hewlett Packard Enterprise)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hpc-and-storage-technology-consultant-at-hewlett-packard-enterprise-4447055132</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Operations Supervisor (Emirates Flight Catering)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-supervisor-at-emirates-flight-catering-4448739084</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Administrative Coordinator (Italian Style General Trading LLC)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-coordinator-at-italian-style-general-trading-llc-4447375594</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IT Executive (Windmills Group)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-executive-at-windmills-group-4448730288</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>⭐ Company Secretary ⭐ (Culture Guru)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%E2%AD%90-company-secretary-%E2%AD%90-at-culture-guru-4450202977</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Technical Director (GRG)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-director-at-grg-4450021623</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Specialist (SKM Air Conditioning LLC)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/talent-acquisition-specialist-at-skm-air-conditioning-llc-4448406217</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -55,6 +55,7 @@
     <sheet name="05-08-2026" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="06-08-2026" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="07-08-2026" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="08-08-2026" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -62058,6 +62059,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Regional Warehouse Operations Officer (Landmark International Auto Spare Parts Trading LLC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-warehouse-operations-officer-at-landmark-international-auto-spare-parts-trading-llc-4448778837</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Supervisor Distribution Center (talabat)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supervisor-distribution-center-at-talabat-4440782654</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warehouse Executive (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-executive-at-rtc1-recruitment-services-4448767796</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Stores Inspector - Jakarta Recruitment Event (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/stores-inspector-jakarta-recruitment-event-at-air-arabia-4450713027</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Stores Controller - Jakarta Recruitment Event (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/stores-controller-jakarta-recruitment-event-at-air-arabia-4450691918</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Team Leader (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/team-leader-at-jd-com-4448765350</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Manager Engineering (talabat)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/manager-engineering-at-talabat-4423961009</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Store Coordinator (Emerson)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-coordinator-at-emerson-4450092872</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Technical Documentation &amp; Document Control Lead (SPM Shipping)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-documentation-document-control-lead-at-spm-shipping-4449205131</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chief Engineer (Hilton)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-engineer-at-hilton-4450728650</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Project Manager (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-manager-at-larsen-toubro-4423002607</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Human Rights Compliance Manager, Human Rights and Social Impact (Amazon)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/human-rights-compliance-manager-human-rights-and-social-impact-at-amazon-4450746401</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Branch Manager (A.A Joyland Pvt. Ltd.)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/branch-manager-at-a-a-joyland-pvt-ltd-4450595078</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>QA/QC Engineer - Infrastructure (Al Marwan Group)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qa-qc-engineer-infrastructure-at-al-marwan-group-4450358765</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Process Engineer (Faham Group)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/process-engineer-at-faham-group-4448748039</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TIC Wire Rope Technical Authority (Motive Offshore Group Ltd)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/tic-wire-rope-technical-authority-at-motive-offshore-group-ltd-4450099415</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EUC Lead / End-User Computing Lead (Tata Consultancy Services)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/euc-lead-end-user-computing-lead-at-tata-consultancy-services-4450320588</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Engine Overhaul Engineer II (Emiratisation) - Engine Workshop (Emirates)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engine-overhaul-engineer-ii-emiratisation-engine-workshop-at-emirates-4448765474</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Parts Picker | Al- Futtaim Automotive | CJDR (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/parts-picker-al-futtaim-automotive-cjdr-at-al-futtaim-4450090995</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Efficiency &amp; Design Assurance Lead (Helios Towers)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/efficiency-design-assurance-lead-at-helios-towers-4435127183</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Group Administrator: Regulatory and Quality Applications (Aspen Pharma Group)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/group-administrator-regulatory-and-quality-applications-at-aspen-pharma-group-4413442119</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Global Mobility &amp; Immigration Specialist – Middle East, EMEA &amp; APAC (Nutanix)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/global-mobility-immigration-specialist-%E2%80%93-middle-east-emea-apac-at-nutanix-4450730923</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Owner (Paragon Construction Zambia)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/owner-at-paragon-construction-zambia-4449203868</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Local Purchase Admin (Chef Middle East)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/local-purchase-admin-at-chef-middle-east-4448778452</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Joint Movements &amp; Travel Specialist (Defence) (Serco)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/joint-movements-travel-specialist-defence-at-serco-4448744967</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -56,6 +56,7 @@
     <sheet name="06-08-2026" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="07-08-2026" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="08-08-2026" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="09-08-2026" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65051,6 +65052,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QAQC CIVIL ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qaqc-civil-engineer-at-larsen-toubro-4414602231</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Engineering Manager (talabat)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-at-talabat-4389532827</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cabin Crew Manager - Sharjah (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cabin-crew-manager-sharjah-at-air-arabia-4432950934</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Supply Chain Manager (Magnum Footwear)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-manager-at-magnum-footwear-4449502084</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>OCC Duty Manager (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/occ-duty-manager-at-air-arabia-4423389620</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Costing Manager (ZULEKHA HOSPITAL)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/costing-manager-at-zulekha-hospital-4449245457</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TESTING ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/testing-engineer-at-larsen-toubro-4442459567</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Housekeeping Manager | UAE (Caviar Careers)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/housekeeping-manager-uae-at-caviar-careers-4451306447</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Efficiency &amp; Design Assurance Lead (Helios Towers)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/efficiency-design-assurance-lead-at-helios-towers-4435127183</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Office Assistan (Afrique Mobilités)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-assistan-at-afrique-mobilit%C3%A9s-4450949215</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Co-Founder (Aurumaxis Labs)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/co-founder-at-aurumaxis-labs-4448005118</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IT Operations Officer (Carra)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-operations-officer-at-carra-4450936497</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Proposal/Planning Coordinator (Bombardier)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/proposal-planning-coordinator-at-bombardier-4414690182</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Government Escalation Advisor (Tamara)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/government-escalation-advisor-at-tamara-4444545630</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Executive Assistant (Edarabia India)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/executive-assistant-at-edarabia-india-4451315561</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Nursery Manager (Green Grass Nursery)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/nursery-manager-at-green-grass-nursery-4449272685</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Installation &amp; Commissioning Engineer (AMS International UAE)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/installation-commissioning-engineer-at-ams-international-uae-4451074643</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Product Engineer for Commissioning &amp; Operations - Global Data Center (Eaton)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/product-engineer-for-commissioning-operations-global-data-center-at-eaton-4401947610</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT Supervisor (Marriott International)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-supervisor-at-marriott-international-4450599935</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Carpenter Foreman (Whizz HR)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/carpenter-foreman-at-whizz-hr-4451084781</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Stewarding Team Leader (SO/ Uptown Dubai)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/stewarding-team-leader-at-so-uptown-dubai-4449259032</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sales Engineer (Edarabia India)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sales-engineer-at-edarabia-india-4451321322</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F5 Managed Services Engineer (Junior) (VaporVM)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/f5-managed-services-engineer-junior-at-vaporvm-4450900366</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Network Engineer (EZSVS MENA Company FZCO)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Process &amp; Maintenance Technician-PCBA (Eaton)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/process-maintenance-technician-pcba-at-eaton-4449254504</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -57,6 +57,7 @@
     <sheet name="07-08-2026" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="08-08-2026" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="09-08-2026" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="10-08-2026" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66548,6 +66549,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workshop Planning Engineer (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-planning-engineer-at-air-arabia-4404092820</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Butchery Supervisor - Distribution Center (talabat)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/butchery-supervisor-distribution-center-at-talabat-4391943600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QAQC CIVIL ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/qaqc-civil-engineer-at-larsen-toubro-4414224930</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Store Manager (MINIMALIST)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-manager-at-minimalist-4449548062</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Engineering  Manager (talabat)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-manager-at-talabat-4385227849</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Facilities &amp; Services Officer (Aldar Education)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-services-officer-at-aldar-education-3929440388</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technical Authority Expert (Ericsson)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-authority-expert-at-ericsson-4450956035</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Process Engineer | alfanar Electric (alfanar)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/process-engineer-alfanar-electric-at-alfanar-4450946637</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Operations Manager - MOE (CHANEL)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-manager-moe-at-chanel-4404783587</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Buyer (Project Based) (Nabors Industries)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/buyer-project-based-at-nabors-industries-4451380676</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Associate Manager - Internal Audit (BEEAH Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/associate-manager-internal-audit-at-beeah-group-4449536397</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Director of Volunteer Management - UAE National (Ministry of Community Empowerment)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/director-of-volunteer-management-uae-national-at-ministry-of-community-empowerment-4438571688</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Procurement Specialist / Purchasing Specialist / Sourcing Specialist (Grow Omaha)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-specialist-purchasing-specialist-sourcing-specialist-at-grow-omaha-4449530697</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Workforce Transformation Specialist (Adecco)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workforce-transformation-specialist-at-adecco-4440541370</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supply Chain – Logistics – Coordinator (Africa Lighthouse Capital)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/supply-chain-%E2%80%93-logistics-%E2%80%93-coordinator-at-africa-lighthouse-capital-4449545354</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mechanical Installation Lead (Vanderlande)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mechanical-installation-lead-at-vanderlande-4365968541</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Restaurants Officer - Food and Beverage (Hays)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/restaurants-officer-food-and-beverage-at-hays-4449542149</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Laundry Supervisor (Sivaay Group ( Managed by SMH Infinity Investment LLC))</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/laundry-supervisor-at-sivaay-group-managed-by-smh-infinity-investment-llc-4449535611</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Principal Materials &amp; Coatings Engineer (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/principal-materials-coatings-engineer-at-mcdermott-international-ltd-4414916731</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>客户支持 (CoinW)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%E5%AE%A2%E6%88%B7%E6%94%AF%E6%8C%81-at-coinw-4440011492</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Client Manager (JD.COM)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/client-manager-at-jd-com-4414901060</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Administrative Assistant (Frío Sparkling Water)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrative-assistant-at-fr%C3%ADo-sparkling-water-4449547215</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Group Director- Strategy &amp; Technology Operations (DP World)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/group-director-strategy-technology-operations-at-dp-world-4433876871</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Maintenance Mechatronics Engineer (Eaton)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-mechatronics-engineer-at-eaton-4430606917</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Client Experience Executive (Dogwalk)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/client-experience-executive-at-dogwalk-4449525696</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -58,6 +58,7 @@
     <sheet name="08-08-2026" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="09-08-2026" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="10-08-2026" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="11-08-2026" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -68045,6 +68046,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Camp Boss (Arada)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/camp-boss-at-arada-4449554995</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Zutari Site Supervision Careers – Infrastructure Projects (Dubai &amp; Abu Dhabi) (Zutari)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/zutari-site-supervision-careers-%E2%80%93-infrastructure-projects-dubai-abu-dhabi-at-zutari-4452188810</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Chief Specialist - Vehicles Technical Inspection (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-specialist-vehicles-technical-inspection-at-roads-and-transport-authority-4438095294</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Operations Executive, (UAE National), Amazon Now, UFG (Amazon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-uae-national-amazon-now-ufg-at-amazon-4452082714</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACES Specialist - UAE National , ACES (Amazon)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/aces-specialist-uae-national-aces-at-amazon-4451813216</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Warranty Administrator | Al-Futtaim Automotive | Electric Mobility (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warranty-administrator-al-futtaim-automotive-electric-mobility-at-al-futtaim-4442708061</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Maintenance Coordinator (Wasco)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-coordinator-at-wasco-4451498746</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Facilities Specialist (ELSEWEDY ELECTRIC)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-specialist-at-elsewedy-electric-4451178475</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MPD Supervisor (Noble Corporation)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mpd-supervisor-at-noble-corporation-4283418131</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Warehouse Manager (In-charge) (Mohamed Hilal Group)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-manager-in-charge-at-mohamed-hilal-group-4451193565</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Logistics Executive - UAE National (Spectrum Industries)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-executive-uae-national-at-spectrum-industries-4452199132</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Officer - Technical Services (flydubai)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-officer-technical-services-at-flydubai-4442562163</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Outbound Operations Administrator (Kingston Stanley)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/outbound-operations-administrator-at-kingston-stanley-4451168699</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nursery Manager (Head of Early Years)-Sharjah (Jumeirah International Nurseries)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/nursery-manager-head-of-early-years-sharjah-at-jumeirah-international-nurseries-4451398816</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DevOps Engineer — Dubai (Jungle Gaming)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/devops-engineer-%E2%80%94-dubai-at-jungle-gaming-4449817043</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chief Specialist - Service Providers (Roads and Transport Authority)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-specialist-service-providers-at-roads-and-transport-authority-4438097218</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zutari Site Supervision Careers – Infrastructure Projects (Dubai &amp; Abu Dhabi) (Zutari)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://eg.linkedin.com/jobs/view/zutari-site-supervision-careers-%E2%80%93-infrastructure-projects-dubai-abu-dhabi-at-zutari-4452178971</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Food Safety Supervisor (GMG)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/food-safety-supervisor-at-gmg-4451623548</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>🇦🇪 Site Engineer | Mega Construction Projects | Dubai, UAE | Turn Engineering into Reality. Build Where the World Looks (Ali Professional)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/%F0%9F%87%A6%F0%9F%87%AA-site-engineer-mega-construction-projects-dubai-uae-turn-engineering-into-reality-build-where-the-world-looks-at-ali-professional-4451501729</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Application Engineer II (Honeywell Technologies)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/application-engineer-ii-at-honeywell-technologies-4451523504</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Quality Ops Tech (McDermott International, Ltd)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/quality-ops-tech-at-mcdermott-international-ltd-4374128856</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Workshop Administrator | Al-Futtaim Automotive | Electric Mobility (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/workshop-administrator-al-futtaim-automotive-electric-mobility-at-al-futtaim-4442598499</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HSSE Technical Assistant (Kent)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/hsse-technical-assistant-at-kent-4452196974</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Logistics and Administration Coordinator (Emirates)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-and-administration-coordinator-at-emirates-4449818021</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Project Delivery &amp; Installation Quality Specialist (Parker Connect)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-delivery-installation-quality-specialist-at-parker-connect-4449555576</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -59,6 +59,7 @@
     <sheet name="09-08-2026" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="10-08-2026" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="11-08-2026" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="12-08-2026" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69542,6 +69543,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Facility Specialist (Mammoet)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facility-specialist-at-mammoet-4443332175</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Engineer Planning &amp; Scheduling (EtihadWE)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineer-planning-scheduling-at-etihadwe-4453057169</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Authorized Service Partner Controller (ASUS)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/authorized-service-partner-controller-at-asus-4451679423</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Logistics Executive, Deliverty Partner Manager (Amazon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-executive-deliverty-partner-manager-at-amazon-4443036037</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Procurement Manager - BESS (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/procurement-manager-bess-at-larsen-toubro-4449868724</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor - UAE National (Amazon)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-uae-national-at-amazon-4443031697</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cargo Revenue Optimization Executive (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cargo-revenue-optimization-executive-at-air-arabia-4451653307</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Assistant Store Supervisor (talabat)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-store-supervisor-at-talabat-4425805516</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Storekeeper (Resolute Dynamics)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-at-resolute-dynamics-4451658953</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Coordinator – Tools Crib (AMC) (flydubai)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/coordinator-%E2%80%93-tools-crib-amc-at-flydubai-4453018453</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Assistant Manager - Warehouse Operations (Confidential)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-warehouse-operations-at-confidential-4451664281</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Production Engineer (SKM Air Conditioning LLC)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-production-engineer-at-skm-air-conditioning-llc-4453058211</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Pricing / Logistic Specialist (Ocean Gate Line)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/pricing-logistic-specialist-at-ocean-gate-line-4452450304</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Progressive)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-progressive-4451630924</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer/Executive Director (Tamer Services Company)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-executive-officer-executive-director-at-tamer-services-company-4450120264</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Storekeeper (Americana Foods)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/storekeeper-at-americana-foods-4449842617</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Projects (Al Ghurair)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-engineer-projects-at-al-ghurair-4451685810</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr. Coordinator Quality Control - Fresh Food (talabat)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/sr-coordinator-quality-control-fresh-food-at-talabat-4452423279</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Stakeholder Manager - JR26TE38 (TRACTEBEL)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/stakeholder-manager-jr26te38-at-tractebel-4452437196</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Maintenance Supervisor (Staff Connect UAE)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/maintenance-supervisor-at-staff-connect-uae-4452375246</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Entry Executive (Zahr Freighters)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-entry-executive-at-zahr-freighters-4452605417</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tendering Engineer (Confidential)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/tendering-engineer-at-confidential-4451635724</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Head - Logistics &amp; Distribution Centre Operations (Genius HRTech Services L.L.C - FZ - Dubai)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-logistics-distribution-centre-operations-at-genius-hrtech-services-l-l-c-fz-dubai-4451906560</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>General Manager (vodavoda mineral water)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Executive - Bids &amp; Estimation (Ejadah)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-bids-estimation-at-ejadah-4449853428</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -60,6 +60,7 @@
     <sheet name="10-08-2026" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="11-08-2026" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="12-08-2026" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="13-08-2026" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -71039,6 +71040,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Store Leadership (talabat)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-leadership-at-talabat-4452375585</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Document Controller (AESG)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-aesg-4453094981</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IT Infrastructure Executive (Parker Connect)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/it-infrastructure-executive-at-parker-connect-4450451641</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Store Auditor (Azizi Developments)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/store-auditor-at-azizi-developments-4450109484</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(National Talent) - Senior Executive – Facility Operations - Global Village - Dubai Holding Entertainment (Global Village, Dubai)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/national-talent-senior-executive-%E2%80%93-facility-operations-global-village-dubai-holding-entertainment-at-global-village-dubai-4453096256</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Human Resources Specialist (Global Lubricant Industry LLC)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/human-resources-specialist-at-global-lubricant-industry-llc-4450106437</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Material Planner (ABB)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/material-planner-at-abb-4449652816</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Office Manager (Ejadah)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-ejadah-4450173183</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Production Incharge ()</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineering Shift Leader (Pullman Hotels &amp; Resorts)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/engineering-shift-leader-at-pullman-hotels-resorts-4452749478</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Contracts Engineer (HREdge Human Resources Consultancy)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/contracts-engineer-at-hredge-human-resources-consultancy-4450177014</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Outbound Operations Administrator (Kingston Stanley)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/outbound-operations-administrator-at-kingston-stanley-4452390074</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Facilities, Atlantis The Royal (Atlantis Resorts)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-facilities-atlantis-the-royal-at-atlantis-resorts-4450138502</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Information Technology Specialist (Nova International General Contracting L.L.C)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-technology-specialist-at-nova-international-general-contracting-l-l-c-4453356396</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MEP Supervisor (Taqweem Technical Services TTS)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/mep-supervisor-at-taqweem-technical-services-tts-4450450601</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Projects (Al Ghurair)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-engineer-projects-at-al-ghurair-4451685810</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zoho Admin (SEVEN)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/zoho-admin-at-seven-4452928113</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Key Quality Controller (Eaton)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/key-quality-controller-at-eaton-4431522111</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Materials Engineer (Mott MacDonald)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/materials-engineer-at-mott-macdonald-4443366169</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Regional Technical &amp; Training Manager (Elite Group Holding)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/regional-technical-training-manager-at-elite-group-holding-4450460413</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Junior AI Support Specialist (Arabian Private Holdings)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/junior-ai-support-specialist-at-arabian-private-holdings-4452378970</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Head of Technical Support (UAE National) (Dicetek LLC)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/head-of-technical-support-uae-national-at-dicetek-llc-4453392824</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>代理 (spark mene)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cost Clerk | Al-Futtaim Electric Mobility | BYD (Al-Futtaim)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/cost-clerk-al-futtaim-electric-mobility-byd-at-al-futtaim-4453156220</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Facility Manager – Owners Association (Real Estate Development)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://linkedin.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -61,6 +61,7 @@
     <sheet name="11-08-2026" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="12-08-2026" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="13-08-2026" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="14-08-2026" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -72536,6 +72537,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Operations Executive, (UAE National), Amazon Now, UFG (Amazon)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-executive-uae-national-amazon-now-ufg-at-amazon-4453691919</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Service Coordinator - Dubai (Rapiscan Systems)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/service-coordinator-dubai-at-rapiscan-systems-4432378899</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B1 - Certifying Engineer - Base Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/b1-certifying-engineer-base-maintenance-at-air-arabia-4426335805</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Warehouse Operations (Nestlé)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/assistant-manager-warehouse-operations-at-nestl%C3%A9-4454001362</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Document Controller (Khazna Data Centers)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/document-controller-at-khazna-data-centers-4331080313</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Facilities Supervisor (Tech Estate Ops)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-supervisor-at-tech-estate-ops-4450463986</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Facilities Management Expert (Talents Tide)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-management-expert-at-talents-tide-4453234298</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Quality &amp; Compliance Specialist-Senior (FedEx)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/quality-compliance-specialist-senior-at-fedex-4454001908</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Executive Supply Chain (Sharaf DG)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/senior-executive-supply-chain-at-sharaf-dg-4454027161</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Technical Specialist (BEEAH Group)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-specialist-at-beeah-group-4450460831</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet Manager – FMCG &amp; Logistics (Parker Connect)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/fleet-manager-%E2%80%93-fmcg-logistics-at-parker-connect-4450459742</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technical Account Management-Dubai (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-account-management-dubai-at-alibaba-cloud-4432770249</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Project Business Material Manager (Hilti Emirates)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-business-material-manager-at-hilti-emirates-4441005080</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Training manager (Xad Technologies)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/training-manager-at-xad-technologies-4452931489</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Operations Engineer (SAS Admin &amp; Kubernetes) (Hexaware Technologies)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-engineer-sas-admin-kubernetes-at-hexaware-technologies-4452920633</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Project Engineer (Azizi Developments)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/project-engineer-at-azizi-developments-4450897004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Information Manager (AtkinsRéalis)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/information-manager-at-atkinsr%C3%A9alis-4452452231</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Technical Account Manager - Openshift- (Remote, Dubai) (Red Hat)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-account-manager-openshift-remote-dubai-at-red-hat-4452994384</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Technical Services Engineer I - Cabin Upgrades and Reconfigurations (Inflight Entertainment and Connectivity) (Emirates)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-services-engineer-i-cabin-upgrades-and-reconfigurations-inflight-entertainment-and-connectivity-at-emirates-4450807684</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward Deployed AI Integrator (UAE National Only), Field Engineering (Amazon Web Services (AWS))</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/forward-deployed-ai-integrator-uae-national-only-field-engineering-at-amazon-web-services-aws-4454358878</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SkyCargo Contact Centre Operations Officer - Emiratisation (Emirates)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/skycargo-contact-centre-operations-officer-emiratisation-at-emirates-4450806627</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Metals Operator (MAN Corp)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/metals-operator-at-man-corp-4452910797</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer (Hidden Talent)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/chief-operating-officer-at-hidden-talent-4453686873</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Operations &amp; Asset Performance Assistant Manager (Enova by Veolia)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-asset-performance-assistant-manager-at-enova-by-veolia-4450496547</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operations Coordinator 1 (TÜV SÜD)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/operations-coordinator-1-at-t%C3%BCv-s%C3%BCd-4450463982</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/dubai_job_tracker.xlsx
+++ b/dubai_job_tracker.xlsx
@@ -62,6 +62,7 @@
     <sheet name="12-08-2026" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="13-08-2026" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="14-08-2026" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="15-08-2026" sheetId="56" state="visible" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74033,6 +74034,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Workplace</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Ind</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Expiry Date</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Job Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Data Center Facility Manager-Dubai (Alibaba Cloud)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/data-center-facility-manager-dubai-at-alibaba-cloud-4423621257</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Warehouse Supervisor (DuPod)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-supervisor-at-dupod-4453564387</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Customer Service Executive-CS&amp;L (Adecco)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/customer-service-executive-cs-l-at-adecco-4454399545</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Logistics Supervisor (Amazon)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-supervisor-at-amazon-4454811943</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B1 - Certifying Engineer - Line Maintenance (Air Arabia)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/b1-certifying-engineer-line-maintenance-at-air-arabia-4423352154</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Office Manager (RTC1 Recruitment Services)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/office-manager-at-rtc1-recruitment-services-4451224420</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Administrator - Logistics &amp; Inventory (Indigo Living)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrator-logistics-inventory-at-indigo-living-4451217762</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Administrator - Logistics &amp; Inventory (Indigo Living UAE)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/administrator-logistics-inventory-at-indigo-living-uae-4450896742</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Warehouse Manager (Protectol Health)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/warehouse-manager-at-protectol-health-4450885353</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TESTING ENGINEER (Larsen &amp; Toubro)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/testing-engineer-at-larsen-toubro-4427006060</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Facilities Manager (Drool Group)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/facilities-manager-at-drool-group-4451224406</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Technical Services Executive - MEA (Aman)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/technical-services-executive-mea-at-aman-4454386566</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>See job details on LinkedIn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sourced via LinkedIn Professional Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Relevant Background / Degree</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ASAP</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Posted Today</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator (Astro Offshore - An Adani Group Company.)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Apply via LinkedIn: https://ae.linkedin.com/jobs/view/logistics-coordinator-at-astro-offshore-an-adani-group-company-4451200552</t>
+      